--- a/BUNT_finance/분트_인건비관리_v2.xlsx
+++ b/BUNT_finance/분트_인건비관리_v2.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직원 마스터" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근무 기록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="급여 요약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지급 이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="급여 요약" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'근무 기록'!$A$1:$H$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'지급 이력'!$A$1:$C$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -60,7 +62,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +87,18 @@
         <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -104,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -131,6 +145,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8513,6 +8539,569 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>지급여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n">
+        <v>202501</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>유은비</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>202501</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>장예원</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>202501</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>202502</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>유은비</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>202502</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>장예원</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>202502</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>202502</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>202503</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>장예원</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>202503</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>202503</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>202504</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>장예원</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>202504</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>202504</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>202505</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>장예원</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>202505</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>202505</v>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>202506</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>202506</v>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>장예원</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>202506</v>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>202506</v>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>202507</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>202507</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>202507</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>202508</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>202508</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>202508</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>202509</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>202509</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>202509</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>202510</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>이진화</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>202510</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>202510</v>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>202511</v>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>이진화</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>202511</v>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>202511</v>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8533,21 +9122,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="10" t="n">
+      <c r="B1" s="14" t="n">
         <v>202502</v>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>← 월 선택</t>
         </is>
       </c>
-      <c r="J1" s="12">
+      <c r="J1" s="16">
         <f>DATE(INT(B1/100),MOD(B1,100),1)</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="J2" s="12">
+      <c r="J2" s="16">
         <f>EOMONTH(J1,0)</f>
         <v/>
       </c>
@@ -8624,8 +9213,8 @@
         <f>IF(B4="","",'직원 마스터'!D2)</f>
         <v/>
       </c>
-      <c r="I4" s="13">
-        <f>IF(B4="","","X")</f>
+      <c r="I4" s="17">
+        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B4)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8658,8 +9247,8 @@
         <f>IF(B5="","",'직원 마스터'!D3)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
-        <f>IF(B5="","","X")</f>
+      <c r="I5" s="17">
+        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B5)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8692,8 +9281,8 @@
         <f>IF(B6="","",'직원 마스터'!D4)</f>
         <v/>
       </c>
-      <c r="I6" s="13">
-        <f>IF(B6="","","X")</f>
+      <c r="I6" s="17">
+        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B6)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8726,8 +9315,8 @@
         <f>IF(B7="","",'직원 마스터'!D5)</f>
         <v/>
       </c>
-      <c r="I7" s="13">
-        <f>IF(B7="","","X")</f>
+      <c r="I7" s="17">
+        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B7)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8760,8 +9349,8 @@
         <f>IF(B8="","",'직원 마스터'!D6)</f>
         <v/>
       </c>
-      <c r="I8" s="13">
-        <f>IF(B8="","","X")</f>
+      <c r="I8" s="17">
+        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B8)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8794,8 +9383,8 @@
         <f>IF(B9="","",'직원 마스터'!D7)</f>
         <v/>
       </c>
-      <c r="I9" s="13">
-        <f>IF(B9="","","X")</f>
+      <c r="I9" s="17">
+        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B9)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8828,8 +9417,8 @@
         <f>IF(B10="","",'직원 마스터'!D8)</f>
         <v/>
       </c>
-      <c r="I10" s="13">
-        <f>IF(B10="","","X")</f>
+      <c r="I10" s="17">
+        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B10)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -8862,37 +9451,37 @@
         <f>IF(B11="","",'직원 마스터'!D9)</f>
         <v/>
       </c>
-      <c r="I11" s="13">
-        <f>IF(B11="","","X")</f>
+      <c r="I11" s="17">
+        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B11)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="19">
         <f>SUM(E4:E11)</f>
         <v/>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="19">
         <f>SUM(F4:F11)</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="19">
         <f>SUM(G4:G11)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>당월 총 인건비</t>
         </is>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="21">
         <f>E13</f>
         <v/>
       </c>

--- a/BUNT_finance/분트_인건비관리_v2.xlsx
+++ b/BUNT_finance/분트_인건비관리_v2.xlsx
@@ -8764,107 +8764,107 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>고경민</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
         <v>202505</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>장예원</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="11" t="n">
         <v>202505</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>전민아</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="11" t="n">
         <v>202505</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>고경민</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
         <v>202506</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>김채현</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="11" t="n">
         <v>202506</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>장예원</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="11" t="n">
         <v>202506</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>전민아</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="11" t="n">
         <v>202506</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>

--- a/BUNT_finance/분트_인건비관리_v2.xlsx
+++ b/BUNT_finance/분트_인건비관리_v2.xlsx
@@ -9198,7 +9198,7 @@
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>IF(B4="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C4="월급",'직원 마스터'!C2,0)))</f>
+        <f>IF(B4="","",IF(C4="월급",'직원 마스터'!C2,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F4" s="9">
@@ -9232,7 +9232,7 @@
         <v/>
       </c>
       <c r="E5" s="9">
-        <f>IF(B5="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C5="월급",'직원 마스터'!C3,0)))</f>
+        <f>IF(B5="","",IF(C5="월급",'직원 마스터'!C3,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F5" s="9">
@@ -9266,7 +9266,7 @@
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>IF(B6="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C6="월급",'직원 마스터'!C4,0)))</f>
+        <f>IF(B6="","",IF(C6="월급",'직원 마스터'!C4,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -9300,7 +9300,7 @@
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>IF(B7="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C7="월급",'직원 마스터'!C5,0)))</f>
+        <f>IF(B7="","",IF(C7="월급",'직원 마스터'!C5,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -9334,7 +9334,7 @@
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IF(B8="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C8="월급",'직원 마스터'!C6,0)))</f>
+        <f>IF(B8="","",IF(C8="월급",'직원 마스터'!C6,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F8" s="9">
@@ -9368,7 +9368,7 @@
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IF(B9="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C9="월급",'직원 마스터'!C7,0)))</f>
+        <f>IF(B9="","",IF(C9="월급",'직원 마스터'!C7,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -9402,7 +9402,7 @@
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IF(B10="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C10="월급",'직원 마스터'!C8,0)))</f>
+        <f>IF(B10="","",IF(C10="월급",'직원 마스터'!C8,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -9436,7 +9436,7 @@
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IF(B11="","",IF(SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))&gt;0,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)),IF(C11="월급",'직원 마스터'!C9,0)))</f>
+        <f>IF(B11="","",IF(C11="월급",'직원 마스터'!C9,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
         <v/>
       </c>
       <c r="F11" s="9">

--- a/BUNT_finance/분트_인건비관리_v2.xlsx
+++ b/BUNT_finance/분트_인건비관리_v2.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -780,11 +780,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>시급</t>
+          <t>월급</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>12000</v>
+        <v>600000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -797,60 +797,62 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>202503</v>
-      </c>
-      <c r="G7" s="4" t="n"/>
+        <v>202502</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>202502</v>
+      </c>
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>시급</t>
+          <t>월급</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12000</v>
+        <v>1800000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>우리은행 1002-351-542250</t>
+          <t>하나은행 558-910330-30707</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>퇴직</t>
+          <t>재직</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>202507</v>
+        <v>202503</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>202510</v>
+        <v>202509</v>
       </c>
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>이진화</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>시급</t>
+          <t>월급</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>12000</v>
+        <v>1848000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>우리은행 1002-166-678383</t>
+          <t>하나은행 558-910330-30707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -859,17 +861,79 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>202511</v>
+        <v>202510</v>
       </c>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="2" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>시급</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>우리은행 1002-351-542250</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>퇴직</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>202507</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>202510</v>
+      </c>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>이진화</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>시급</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>우리은행 1002-166-678383</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>재직</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>202511</v>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="월급 또는 시급만 입력 가능합니다" type="list">
+    <dataValidation sqref="B2:B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="월급 또는 시급만 입력 가능합니다" type="list">
       <formula1>"월급,시급"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"재직,퇴직"</formula1>
     </dataValidation>
   </dataValidations>
@@ -962,7 +1026,7 @@
         <v>72000</v>
       </c>
       <c r="G2" s="8">
-        <f>IFERROR(IF(B2&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B2)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A2)*100+MONTH(A2)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A2)*100+MONTH(A2)))),0)),""),"")</f>
+        <f>IFERROR(IF(B2&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B2)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A2)*100+MONTH(A2)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A2)*100+MONTH(A2)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -990,7 +1054,7 @@
         <v>48000</v>
       </c>
       <c r="G3" s="8">
-        <f>IFERROR(IF(B3&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B3)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A3)*100+MONTH(A3)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A3)*100+MONTH(A3)))),0)),""),"")</f>
+        <f>IFERROR(IF(B3&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B3)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A3)*100+MONTH(A3)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A3)*100+MONTH(A3)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1018,7 +1082,7 @@
         <v>48000</v>
       </c>
       <c r="G4" s="8">
-        <f>IFERROR(IF(B4&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B4)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A4)*100+MONTH(A4)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A4)*100+MONTH(A4)))),0)),""),"")</f>
+        <f>IFERROR(IF(B4&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B4)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A4)*100+MONTH(A4)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A4)*100+MONTH(A4)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -1046,7 +1110,7 @@
         <v>48000</v>
       </c>
       <c r="G5" s="8">
-        <f>IFERROR(IF(B5&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B5)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A5)*100+MONTH(A5)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A5)*100+MONTH(A5)))),0)),""),"")</f>
+        <f>IFERROR(IF(B5&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B5)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A5)*100+MONTH(A5)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A5)*100+MONTH(A5)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H5" s="2" t="n"/>
@@ -1074,7 +1138,7 @@
         <v>48000</v>
       </c>
       <c r="G6" s="8">
-        <f>IFERROR(IF(B6&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B6)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A6)*100+MONTH(A6)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A6)*100+MONTH(A6)))),0)),""),"")</f>
+        <f>IFERROR(IF(B6&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B6)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A6)*100+MONTH(A6)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A6)*100+MONTH(A6)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H6" s="2" t="n"/>
@@ -1102,7 +1166,7 @@
         <v>48000</v>
       </c>
       <c r="G7" s="8">
-        <f>IFERROR(IF(B7&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B7)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A7)*100+MONTH(A7)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A7)*100+MONTH(A7)))),0)),""),"")</f>
+        <f>IFERROR(IF(B7&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B7)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A7)*100+MONTH(A7)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A7)*100+MONTH(A7)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H7" s="2" t="n"/>
@@ -1130,7 +1194,7 @@
         <v>72000</v>
       </c>
       <c r="G8" s="8">
-        <f>IFERROR(IF(B8&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B8)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A8)*100+MONTH(A8)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A8)*100+MONTH(A8)))),0)),""),"")</f>
+        <f>IFERROR(IF(B8&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B8)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A8)*100+MONTH(A8)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A8)*100+MONTH(A8)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H8" s="2" t="n"/>
@@ -1158,7 +1222,7 @@
         <v>48000</v>
       </c>
       <c r="G9" s="8">
-        <f>IFERROR(IF(B9&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B9)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A9)*100+MONTH(A9)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A9)*100+MONTH(A9)))),0)),""),"")</f>
+        <f>IFERROR(IF(B9&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B9)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A9)*100+MONTH(A9)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A9)*100+MONTH(A9)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H9" s="2" t="n"/>
@@ -1186,7 +1250,7 @@
         <v>48000</v>
       </c>
       <c r="G10" s="8">
-        <f>IFERROR(IF(B10&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B10)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A10)*100+MONTH(A10)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A10)*100+MONTH(A10)))),0)),""),"")</f>
+        <f>IFERROR(IF(B10&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B10)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A10)*100+MONTH(A10)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A10)*100+MONTH(A10)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H10" s="2" t="n"/>
@@ -1214,7 +1278,7 @@
         <v>48000</v>
       </c>
       <c r="G11" s="8">
-        <f>IFERROR(IF(B11&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B11)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A11)*100+MONTH(A11)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A11)*100+MONTH(A11)))),0)),""),"")</f>
+        <f>IFERROR(IF(B11&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B11)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A11)*100+MONTH(A11)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A11)*100+MONTH(A11)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H11" s="2" t="n"/>
@@ -1242,7 +1306,7 @@
         <v>48000</v>
       </c>
       <c r="G12" s="8">
-        <f>IFERROR(IF(B12&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B12)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A12)*100+MONTH(A12)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A12)*100+MONTH(A12)))),0)),""),"")</f>
+        <f>IFERROR(IF(B12&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B12)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A12)*100+MONTH(A12)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A12)*100+MONTH(A12)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -1270,7 +1334,7 @@
         <v>48000</v>
       </c>
       <c r="G13" s="8">
-        <f>IFERROR(IF(B13&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B13)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A13)*100+MONTH(A13)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A13)*100+MONTH(A13)))),0)),""),"")</f>
+        <f>IFERROR(IF(B13&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B13)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A13)*100+MONTH(A13)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A13)*100+MONTH(A13)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H13" s="2" t="n"/>
@@ -1298,7 +1362,7 @@
         <v>72000</v>
       </c>
       <c r="G14" s="8">
-        <f>IFERROR(IF(B14&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B14)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A14)*100+MONTH(A14)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A14)*100+MONTH(A14)))),0)),""),"")</f>
+        <f>IFERROR(IF(B14&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B14)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A14)*100+MONTH(A14)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A14)*100+MONTH(A14)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H14" s="2" t="n"/>
@@ -1326,7 +1390,7 @@
         <v>48000</v>
       </c>
       <c r="G15" s="8">
-        <f>IFERROR(IF(B15&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B15)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A15)*100+MONTH(A15)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A15)*100+MONTH(A15)))),0)),""),"")</f>
+        <f>IFERROR(IF(B15&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B15)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A15)*100+MONTH(A15)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A15)*100+MONTH(A15)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H15" s="2" t="n"/>
@@ -1354,7 +1418,7 @@
         <v>48000</v>
       </c>
       <c r="G16" s="8">
-        <f>IFERROR(IF(B16&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B16)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A16)*100+MONTH(A16)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A16)*100+MONTH(A16)))),0)),""),"")</f>
+        <f>IFERROR(IF(B16&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B16)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A16)*100+MONTH(A16)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A16)*100+MONTH(A16)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H16" s="2" t="n"/>
@@ -1382,7 +1446,7 @@
         <v>48000</v>
       </c>
       <c r="G17" s="8">
-        <f>IFERROR(IF(B17&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B17)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A17)*100+MONTH(A17)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A17)*100+MONTH(A17)))),0)),""),"")</f>
+        <f>IFERROR(IF(B17&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B17)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A17)*100+MONTH(A17)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A17)*100+MONTH(A17)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H17" s="2" t="n"/>
@@ -1410,7 +1474,7 @@
         <v>48000</v>
       </c>
       <c r="G18" s="8">
-        <f>IFERROR(IF(B18&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B18)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A18)*100+MONTH(A18)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A18)*100+MONTH(A18)))),0)),""),"")</f>
+        <f>IFERROR(IF(B18&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B18)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A18)*100+MONTH(A18)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A18)*100+MONTH(A18)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H18" s="2" t="n"/>
@@ -1438,7 +1502,7 @@
         <v>54000</v>
       </c>
       <c r="G19" s="8">
-        <f>IFERROR(IF(B19&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B19)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A19)*100+MONTH(A19)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A19)*100+MONTH(A19)))),0)),""),"")</f>
+        <f>IFERROR(IF(B19&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B19)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A19)*100+MONTH(A19)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A19)*100+MONTH(A19)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H19" s="2" t="n"/>
@@ -1466,7 +1530,7 @@
         <v>72000</v>
       </c>
       <c r="G20" s="8">
-        <f>IFERROR(IF(B20&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B20)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A20)*100+MONTH(A20)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A20)*100+MONTH(A20)))),0)),""),"")</f>
+        <f>IFERROR(IF(B20&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B20)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A20)*100+MONTH(A20)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A20)*100+MONTH(A20)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H20" s="2" t="n"/>
@@ -1494,7 +1558,7 @@
         <v>48000</v>
       </c>
       <c r="G21" s="8">
-        <f>IFERROR(IF(B21&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B21)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A21)*100+MONTH(A21)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A21)*100+MONTH(A21)))),0)),""),"")</f>
+        <f>IFERROR(IF(B21&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B21)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A21)*100+MONTH(A21)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A21)*100+MONTH(A21)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H21" s="2" t="n"/>
@@ -1522,7 +1586,7 @@
         <v>48000</v>
       </c>
       <c r="G22" s="8">
-        <f>IFERROR(IF(B22&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B22)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A22)*100+MONTH(A22)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A22)*100+MONTH(A22)))),0)),""),"")</f>
+        <f>IFERROR(IF(B22&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B22)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A22)*100+MONTH(A22)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A22)*100+MONTH(A22)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H22" s="2" t="n"/>
@@ -1550,7 +1614,7 @@
         <v>60000</v>
       </c>
       <c r="G23" s="8">
-        <f>IFERROR(IF(B23&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B23)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A23)*100+MONTH(A23)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A23)*100+MONTH(A23)))),0)),""),"")</f>
+        <f>IFERROR(IF(B23&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B23)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A23)*100+MONTH(A23)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A23)*100+MONTH(A23)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H23" s="2" t="n"/>
@@ -1578,7 +1642,7 @@
         <v>48000</v>
       </c>
       <c r="G24" s="8">
-        <f>IFERROR(IF(B24&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B24)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A24)*100+MONTH(A24)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A24)*100+MONTH(A24)))),0)),""),"")</f>
+        <f>IFERROR(IF(B24&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B24)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A24)*100+MONTH(A24)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A24)*100+MONTH(A24)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H24" s="2" t="n"/>
@@ -1606,7 +1670,7 @@
         <v>48000</v>
       </c>
       <c r="G25" s="8">
-        <f>IFERROR(IF(B25&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B25)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A25)*100+MONTH(A25)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A25)*100+MONTH(A25)))),0)),""),"")</f>
+        <f>IFERROR(IF(B25&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B25)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A25)*100+MONTH(A25)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A25)*100+MONTH(A25)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H25" s="2" t="n"/>
@@ -1634,7 +1698,7 @@
         <v>72000</v>
       </c>
       <c r="G26" s="8">
-        <f>IFERROR(IF(B26&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B26)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A26)*100+MONTH(A26)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A26)*100+MONTH(A26)))),0)),""),"")</f>
+        <f>IFERROR(IF(B26&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B26)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A26)*100+MONTH(A26)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A26)*100+MONTH(A26)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H26" s="2" t="n"/>
@@ -1662,7 +1726,7 @@
         <v>48000</v>
       </c>
       <c r="G27" s="8">
-        <f>IFERROR(IF(B27&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B27)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A27)*100+MONTH(A27)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A27)*100+MONTH(A27)))),0)),""),"")</f>
+        <f>IFERROR(IF(B27&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B27)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A27)*100+MONTH(A27)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A27)*100+MONTH(A27)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H27" s="2" t="n"/>
@@ -1690,7 +1754,7 @@
         <v>48000</v>
       </c>
       <c r="G28" s="8">
-        <f>IFERROR(IF(B28&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B28)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A28)*100+MONTH(A28)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A28)*100+MONTH(A28)))),0)),""),"")</f>
+        <f>IFERROR(IF(B28&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B28)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A28)*100+MONTH(A28)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A28)*100+MONTH(A28)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H28" s="2" t="n"/>
@@ -1718,7 +1782,7 @@
         <v>48000</v>
       </c>
       <c r="G29" s="8">
-        <f>IFERROR(IF(B29&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B29)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A29)*100+MONTH(A29)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A29)*100+MONTH(A29)))),0)),""),"")</f>
+        <f>IFERROR(IF(B29&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B29)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A29)*100+MONTH(A29)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A29)*100+MONTH(A29)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H29" s="2" t="n"/>
@@ -1746,7 +1810,7 @@
         <v>72000</v>
       </c>
       <c r="G30" s="8">
-        <f>IFERROR(IF(B30&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B30)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A30)*100+MONTH(A30)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A30)*100+MONTH(A30)))),0)),""),"")</f>
+        <f>IFERROR(IF(B30&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B30)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A30)*100+MONTH(A30)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A30)*100+MONTH(A30)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H30" s="2" t="n"/>
@@ -1774,7 +1838,7 @@
         <v>48000</v>
       </c>
       <c r="G31" s="8">
-        <f>IFERROR(IF(B31&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B31)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A31)*100+MONTH(A31)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A31)*100+MONTH(A31)))),0)),""),"")</f>
+        <f>IFERROR(IF(B31&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B31)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A31)*100+MONTH(A31)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A31)*100+MONTH(A31)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H31" s="2" t="n"/>
@@ -1802,7 +1866,7 @@
         <v>48000</v>
       </c>
       <c r="G32" s="8">
-        <f>IFERROR(IF(B32&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B32)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A32)*100+MONTH(A32)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A32)*100+MONTH(A32)))),0)),""),"")</f>
+        <f>IFERROR(IF(B32&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B32)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A32)*100+MONTH(A32)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A32)*100+MONTH(A32)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H32" s="2" t="n"/>
@@ -1830,7 +1894,7 @@
         <v>48000</v>
       </c>
       <c r="G33" s="8">
-        <f>IFERROR(IF(B33&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B33)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A33)*100+MONTH(A33)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A33)*100+MONTH(A33)))),0)),""),"")</f>
+        <f>IFERROR(IF(B33&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B33)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A33)*100+MONTH(A33)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A33)*100+MONTH(A33)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H33" s="2" t="n"/>
@@ -1858,7 +1922,7 @@
         <v>48000</v>
       </c>
       <c r="G34" s="8">
-        <f>IFERROR(IF(B34&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B34)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A34)*100+MONTH(A34)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A34)*100+MONTH(A34)))),0)),""),"")</f>
+        <f>IFERROR(IF(B34&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B34)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A34)*100+MONTH(A34)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A34)*100+MONTH(A34)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H34" s="2" t="n"/>
@@ -1886,7 +1950,7 @@
         <v>48000</v>
       </c>
       <c r="G35" s="8">
-        <f>IFERROR(IF(B35&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B35)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A35)*100+MONTH(A35)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A35)*100+MONTH(A35)))),0)),""),"")</f>
+        <f>IFERROR(IF(B35&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B35)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A35)*100+MONTH(A35)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A35)*100+MONTH(A35)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H35" s="2" t="n"/>
@@ -1914,7 +1978,7 @@
         <v>72000</v>
       </c>
       <c r="G36" s="8">
-        <f>IFERROR(IF(B36&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B36)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A36)*100+MONTH(A36)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A36)*100+MONTH(A36)))),0)),""),"")</f>
+        <f>IFERROR(IF(B36&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B36)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A36)*100+MONTH(A36)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A36)*100+MONTH(A36)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H36" s="2" t="n"/>
@@ -1942,7 +2006,7 @@
         <v>48000</v>
       </c>
       <c r="G37" s="8">
-        <f>IFERROR(IF(B37&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B37)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A37)*100+MONTH(A37)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A37)*100+MONTH(A37)))),0)),""),"")</f>
+        <f>IFERROR(IF(B37&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B37)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A37)*100+MONTH(A37)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A37)*100+MONTH(A37)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H37" s="2" t="n"/>
@@ -1970,7 +2034,7 @@
         <v>72000</v>
       </c>
       <c r="G38" s="8">
-        <f>IFERROR(IF(B38&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B38)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A38)*100+MONTH(A38)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A38)*100+MONTH(A38)))),0)),""),"")</f>
+        <f>IFERROR(IF(B38&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B38)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A38)*100+MONTH(A38)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A38)*100+MONTH(A38)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H38" s="2" t="n"/>
@@ -1998,7 +2062,7 @@
         <v>72000</v>
       </c>
       <c r="G39" s="8">
-        <f>IFERROR(IF(B39&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B39)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A39)*100+MONTH(A39)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A39)*100+MONTH(A39)))),0)),""),"")</f>
+        <f>IFERROR(IF(B39&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B39)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A39)*100+MONTH(A39)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A39)*100+MONTH(A39)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H39" s="2" t="n"/>
@@ -2026,7 +2090,7 @@
         <v>72000</v>
       </c>
       <c r="G40" s="8">
-        <f>IFERROR(IF(B40&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B40)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A40)*100+MONTH(A40)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A40)*100+MONTH(A40)))),0)),""),"")</f>
+        <f>IFERROR(IF(B40&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B40)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A40)*100+MONTH(A40)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A40)*100+MONTH(A40)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H40" s="2" t="n"/>
@@ -2054,7 +2118,7 @@
         <v>48000</v>
       </c>
       <c r="G41" s="8">
-        <f>IFERROR(IF(B41&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B41)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A41)*100+MONTH(A41)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A41)*100+MONTH(A41)))),0)),""),"")</f>
+        <f>IFERROR(IF(B41&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B41)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A41)*100+MONTH(A41)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A41)*100+MONTH(A41)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H41" s="2" t="n"/>
@@ -2082,7 +2146,7 @@
         <v>72000</v>
       </c>
       <c r="G42" s="8">
-        <f>IFERROR(IF(B42&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B42)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A42)*100+MONTH(A42)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A42)*100+MONTH(A42)))),0)),""),"")</f>
+        <f>IFERROR(IF(B42&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B42)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A42)*100+MONTH(A42)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A42)*100+MONTH(A42)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H42" s="2" t="n"/>
@@ -2110,7 +2174,7 @@
         <v>48000</v>
       </c>
       <c r="G43" s="8">
-        <f>IFERROR(IF(B43&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B43)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A43)*100+MONTH(A43)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A43)*100+MONTH(A43)))),0)),""),"")</f>
+        <f>IFERROR(IF(B43&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B43)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A43)*100+MONTH(A43)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A43)*100+MONTH(A43)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H43" s="2" t="n"/>
@@ -2138,7 +2202,7 @@
         <v>60000</v>
       </c>
       <c r="G44" s="8">
-        <f>IFERROR(IF(B44&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B44)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A44)*100+MONTH(A44)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A44)*100+MONTH(A44)))),0)),""),"")</f>
+        <f>IFERROR(IF(B44&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B44)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A44)*100+MONTH(A44)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A44)*100+MONTH(A44)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H44" s="2" t="n"/>
@@ -2166,7 +2230,7 @@
         <v>36000</v>
       </c>
       <c r="G45" s="8">
-        <f>IFERROR(IF(B45&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B45)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A45)*100+MONTH(A45)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A45)*100+MONTH(A45)))),0)),""),"")</f>
+        <f>IFERROR(IF(B45&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B45)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A45)*100+MONTH(A45)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A45)*100+MONTH(A45)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H45" s="2" t="n"/>
@@ -2194,7 +2258,7 @@
         <v>48000</v>
       </c>
       <c r="G46" s="8">
-        <f>IFERROR(IF(B46&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B46)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A46)*100+MONTH(A46)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A46)*100+MONTH(A46)))),0)),""),"")</f>
+        <f>IFERROR(IF(B46&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B46)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A46)*100+MONTH(A46)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A46)*100+MONTH(A46)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H46" s="2" t="n"/>
@@ -2222,7 +2286,7 @@
         <v>48000</v>
       </c>
       <c r="G47" s="8">
-        <f>IFERROR(IF(B47&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B47)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A47)*100+MONTH(A47)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A47)*100+MONTH(A47)))),0)),""),"")</f>
+        <f>IFERROR(IF(B47&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B47)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A47)*100+MONTH(A47)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A47)*100+MONTH(A47)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H47" s="2" t="n"/>
@@ -2250,7 +2314,7 @@
         <v>72000</v>
       </c>
       <c r="G48" s="8">
-        <f>IFERROR(IF(B48&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B48)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A48)*100+MONTH(A48)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A48)*100+MONTH(A48)))),0)),""),"")</f>
+        <f>IFERROR(IF(B48&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B48)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A48)*100+MONTH(A48)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A48)*100+MONTH(A48)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H48" s="2" t="n"/>
@@ -2278,7 +2342,7 @@
         <v>48000</v>
       </c>
       <c r="G49" s="8">
-        <f>IFERROR(IF(B49&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B49)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A49)*100+MONTH(A49)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A49)*100+MONTH(A49)))),0)),""),"")</f>
+        <f>IFERROR(IF(B49&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B49)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A49)*100+MONTH(A49)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A49)*100+MONTH(A49)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H49" s="2" t="n"/>
@@ -2306,7 +2370,7 @@
         <v>60000</v>
       </c>
       <c r="G50" s="8">
-        <f>IFERROR(IF(B50&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B50)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A50)*100+MONTH(A50)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A50)*100+MONTH(A50)))),0)),""),"")</f>
+        <f>IFERROR(IF(B50&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B50)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A50)*100+MONTH(A50)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A50)*100+MONTH(A50)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H50" s="2" t="n"/>
@@ -2334,7 +2398,7 @@
         <v>60000</v>
       </c>
       <c r="G51" s="8">
-        <f>IFERROR(IF(B51&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B51)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A51)*100+MONTH(A51)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A51)*100+MONTH(A51)))),0)),""),"")</f>
+        <f>IFERROR(IF(B51&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B51)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A51)*100+MONTH(A51)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A51)*100+MONTH(A51)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H51" s="2" t="n"/>
@@ -2362,7 +2426,7 @@
         <v>60000</v>
       </c>
       <c r="G52" s="8">
-        <f>IFERROR(IF(B52&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B52)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A52)*100+MONTH(A52)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A52)*100+MONTH(A52)))),0)),""),"")</f>
+        <f>IFERROR(IF(B52&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B52)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A52)*100+MONTH(A52)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A52)*100+MONTH(A52)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H52" s="2" t="n"/>
@@ -2390,7 +2454,7 @@
         <v>60000</v>
       </c>
       <c r="G53" s="8">
-        <f>IFERROR(IF(B53&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B53)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A53)*100+MONTH(A53)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A53)*100+MONTH(A53)))),0)),""),"")</f>
+        <f>IFERROR(IF(B53&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B53)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A53)*100+MONTH(A53)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A53)*100+MONTH(A53)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H53" s="2" t="n"/>
@@ -2418,7 +2482,7 @@
         <v>60000</v>
       </c>
       <c r="G54" s="8">
-        <f>IFERROR(IF(B54&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B54)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A54)*100+MONTH(A54)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A54)*100+MONTH(A54)))),0)),""),"")</f>
+        <f>IFERROR(IF(B54&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B54)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A54)*100+MONTH(A54)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A54)*100+MONTH(A54)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H54" s="2" t="n"/>
@@ -2446,7 +2510,7 @@
         <v>60000</v>
       </c>
       <c r="G55" s="8">
-        <f>IFERROR(IF(B55&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B55)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A55)*100+MONTH(A55)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A55)*100+MONTH(A55)))),0)),""),"")</f>
+        <f>IFERROR(IF(B55&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B55)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A55)*100+MONTH(A55)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A55)*100+MONTH(A55)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H55" s="2" t="n"/>
@@ -2474,7 +2538,7 @@
         <v>60000</v>
       </c>
       <c r="G56" s="8">
-        <f>IFERROR(IF(B56&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B56)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A56)*100+MONTH(A56)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A56)*100+MONTH(A56)))),0)),""),"")</f>
+        <f>IFERROR(IF(B56&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B56)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A56)*100+MONTH(A56)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A56)*100+MONTH(A56)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H56" s="2" t="n"/>
@@ -2502,7 +2566,7 @@
         <v>60000</v>
       </c>
       <c r="G57" s="8">
-        <f>IFERROR(IF(B57&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B57)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A57)*100+MONTH(A57)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A57)*100+MONTH(A57)))),0)),""),"")</f>
+        <f>IFERROR(IF(B57&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B57)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A57)*100+MONTH(A57)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A57)*100+MONTH(A57)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H57" s="2" t="n"/>
@@ -2530,7 +2594,7 @@
         <v>60000</v>
       </c>
       <c r="G58" s="8">
-        <f>IFERROR(IF(B58&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B58)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A58)*100+MONTH(A58)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A58)*100+MONTH(A58)))),0)),""),"")</f>
+        <f>IFERROR(IF(B58&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B58)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A58)*100+MONTH(A58)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A58)*100+MONTH(A58)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H58" s="2" t="n"/>
@@ -2558,7 +2622,7 @@
         <v>48000</v>
       </c>
       <c r="G59" s="8">
-        <f>IFERROR(IF(B59&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B59)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A59)*100+MONTH(A59)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A59)*100+MONTH(A59)))),0)),""),"")</f>
+        <f>IFERROR(IF(B59&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B59)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A59)*100+MONTH(A59)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A59)*100+MONTH(A59)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H59" s="2" t="n"/>
@@ -2586,7 +2650,7 @@
         <v>60000</v>
       </c>
       <c r="G60" s="8">
-        <f>IFERROR(IF(B60&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B60)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A60)*100+MONTH(A60)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A60)*100+MONTH(A60)))),0)),""),"")</f>
+        <f>IFERROR(IF(B60&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B60)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A60)*100+MONTH(A60)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A60)*100+MONTH(A60)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H60" s="2" t="n"/>
@@ -2614,7 +2678,7 @@
         <v>60000</v>
       </c>
       <c r="G61" s="8">
-        <f>IFERROR(IF(B61&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B61)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A61)*100+MONTH(A61)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A61)*100+MONTH(A61)))),0)),""),"")</f>
+        <f>IFERROR(IF(B61&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B61)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A61)*100+MONTH(A61)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A61)*100+MONTH(A61)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H61" s="2" t="n"/>
@@ -2642,7 +2706,7 @@
         <v>60000</v>
       </c>
       <c r="G62" s="8">
-        <f>IFERROR(IF(B62&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B62)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A62)*100+MONTH(A62)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A62)*100+MONTH(A62)))),0)),""),"")</f>
+        <f>IFERROR(IF(B62&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B62)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A62)*100+MONTH(A62)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A62)*100+MONTH(A62)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H62" s="2" t="n"/>
@@ -2670,7 +2734,7 @@
         <v>60000</v>
       </c>
       <c r="G63" s="8">
-        <f>IFERROR(IF(B63&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B63)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A63)*100+MONTH(A63)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A63)*100+MONTH(A63)))),0)),""),"")</f>
+        <f>IFERROR(IF(B63&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B63)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A63)*100+MONTH(A63)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A63)*100+MONTH(A63)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H63" s="2" t="n"/>
@@ -2698,7 +2762,7 @@
         <v>60000</v>
       </c>
       <c r="G64" s="8">
-        <f>IFERROR(IF(B64&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B64)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A64)*100+MONTH(A64)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A64)*100+MONTH(A64)))),0)),""),"")</f>
+        <f>IFERROR(IF(B64&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B64)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A64)*100+MONTH(A64)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A64)*100+MONTH(A64)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H64" s="2" t="n"/>
@@ -2726,7 +2790,7 @@
         <v>48000</v>
       </c>
       <c r="G65" s="8">
-        <f>IFERROR(IF(B65&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B65)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A65)*100+MONTH(A65)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A65)*100+MONTH(A65)))),0)),""),"")</f>
+        <f>IFERROR(IF(B65&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B65)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A65)*100+MONTH(A65)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A65)*100+MONTH(A65)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H65" s="2" t="n"/>
@@ -2754,7 +2818,7 @@
         <v>48000</v>
       </c>
       <c r="G66" s="8">
-        <f>IFERROR(IF(B66&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B66)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A66)*100+MONTH(A66)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A66)*100+MONTH(A66)))),0)),""),"")</f>
+        <f>IFERROR(IF(B66&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B66)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A66)*100+MONTH(A66)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A66)*100+MONTH(A66)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H66" s="2" t="n"/>
@@ -2782,7 +2846,7 @@
         <v>60000</v>
       </c>
       <c r="G67" s="8">
-        <f>IFERROR(IF(B67&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B67)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A67)*100+MONTH(A67)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A67)*100+MONTH(A67)))),0)),""),"")</f>
+        <f>IFERROR(IF(B67&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B67)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A67)*100+MONTH(A67)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A67)*100+MONTH(A67)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H67" s="2" t="n"/>
@@ -2810,7 +2874,7 @@
         <v>60000</v>
       </c>
       <c r="G68" s="8">
-        <f>IFERROR(IF(B68&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B68)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A68)*100+MONTH(A68)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A68)*100+MONTH(A68)))),0)),""),"")</f>
+        <f>IFERROR(IF(B68&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B68)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A68)*100+MONTH(A68)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A68)*100+MONTH(A68)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H68" s="2" t="n"/>
@@ -2838,7 +2902,7 @@
         <v>60000</v>
       </c>
       <c r="G69" s="8">
-        <f>IFERROR(IF(B69&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B69)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A69)*100+MONTH(A69)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A69)*100+MONTH(A69)))),0)),""),"")</f>
+        <f>IFERROR(IF(B69&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B69)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A69)*100+MONTH(A69)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A69)*100+MONTH(A69)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H69" s="2" t="n"/>
@@ -2866,7 +2930,7 @@
         <v>60000</v>
       </c>
       <c r="G70" s="8">
-        <f>IFERROR(IF(B70&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B70)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A70)*100+MONTH(A70)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A70)*100+MONTH(A70)))),0)),""),"")</f>
+        <f>IFERROR(IF(B70&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B70)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A70)*100+MONTH(A70)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A70)*100+MONTH(A70)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H70" s="2" t="n"/>
@@ -2894,7 +2958,7 @@
         <v>36000</v>
       </c>
       <c r="G71" s="8">
-        <f>IFERROR(IF(B71&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B71)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A71)*100+MONTH(A71)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A71)*100+MONTH(A71)))),0)),""),"")</f>
+        <f>IFERROR(IF(B71&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B71)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A71)*100+MONTH(A71)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A71)*100+MONTH(A71)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H71" s="2" t="n"/>
@@ -2922,7 +2986,7 @@
         <v>60000</v>
       </c>
       <c r="G72" s="8">
-        <f>IFERROR(IF(B72&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B72)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A72)*100+MONTH(A72)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A72)*100+MONTH(A72)))),0)),""),"")</f>
+        <f>IFERROR(IF(B72&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B72)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A72)*100+MONTH(A72)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A72)*100+MONTH(A72)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H72" s="2" t="n"/>
@@ -2950,7 +3014,7 @@
         <v>60000</v>
       </c>
       <c r="G73" s="8">
-        <f>IFERROR(IF(B73&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B73)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A73)*100+MONTH(A73)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A73)*100+MONTH(A73)))),0)),""),"")</f>
+        <f>IFERROR(IF(B73&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B73)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A73)*100+MONTH(A73)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A73)*100+MONTH(A73)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H73" s="2" t="n"/>
@@ -2978,7 +3042,7 @@
         <v>60000</v>
       </c>
       <c r="G74" s="8">
-        <f>IFERROR(IF(B74&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B74)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A74)*100+MONTH(A74)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A74)*100+MONTH(A74)))),0)),""),"")</f>
+        <f>IFERROR(IF(B74&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B74)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A74)*100+MONTH(A74)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A74)*100+MONTH(A74)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H74" s="2" t="n"/>
@@ -3006,7 +3070,7 @@
         <v>60000</v>
       </c>
       <c r="G75" s="8">
-        <f>IFERROR(IF(B75&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B75)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A75)*100+MONTH(A75)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A75)*100+MONTH(A75)))),0)),""),"")</f>
+        <f>IFERROR(IF(B75&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B75)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A75)*100+MONTH(A75)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A75)*100+MONTH(A75)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H75" s="2" t="n"/>
@@ -3034,7 +3098,7 @@
         <v>60000</v>
       </c>
       <c r="G76" s="8">
-        <f>IFERROR(IF(B76&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B76)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A76)*100+MONTH(A76)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A76)*100+MONTH(A76)))),0)),""),"")</f>
+        <f>IFERROR(IF(B76&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B76)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A76)*100+MONTH(A76)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A76)*100+MONTH(A76)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H76" s="2" t="n"/>
@@ -3062,7 +3126,7 @@
         <v>48000</v>
       </c>
       <c r="G77" s="8">
-        <f>IFERROR(IF(B77&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B77)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A77)*100+MONTH(A77)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A77)*100+MONTH(A77)))),0)),""),"")</f>
+        <f>IFERROR(IF(B77&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B77)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A77)*100+MONTH(A77)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A77)*100+MONTH(A77)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H77" s="2" t="n"/>
@@ -3090,7 +3154,7 @@
         <v>60000</v>
       </c>
       <c r="G78" s="8">
-        <f>IFERROR(IF(B78&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B78)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A78)*100+MONTH(A78)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A78)*100+MONTH(A78)))),0)),""),"")</f>
+        <f>IFERROR(IF(B78&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B78)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A78)*100+MONTH(A78)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A78)*100+MONTH(A78)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H78" s="2" t="n"/>
@@ -3118,7 +3182,7 @@
         <v>60000</v>
       </c>
       <c r="G79" s="8">
-        <f>IFERROR(IF(B79&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B79)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A79)*100+MONTH(A79)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A79)*100+MONTH(A79)))),0)),""),"")</f>
+        <f>IFERROR(IF(B79&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B79)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A79)*100+MONTH(A79)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A79)*100+MONTH(A79)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H79" s="2" t="n"/>
@@ -3146,7 +3210,7 @@
         <v>60000</v>
       </c>
       <c r="G80" s="8">
-        <f>IFERROR(IF(B80&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B80)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A80)*100+MONTH(A80)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A80)*100+MONTH(A80)))),0)),""),"")</f>
+        <f>IFERROR(IF(B80&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B80)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A80)*100+MONTH(A80)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A80)*100+MONTH(A80)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H80" s="2" t="n"/>
@@ -3174,7 +3238,7 @@
         <v>48000</v>
       </c>
       <c r="G81" s="8">
-        <f>IFERROR(IF(B81&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B81)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A81)*100+MONTH(A81)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A81)*100+MONTH(A81)))),0)),""),"")</f>
+        <f>IFERROR(IF(B81&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B81)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A81)*100+MONTH(A81)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A81)*100+MONTH(A81)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H81" s="2" t="n"/>
@@ -3202,7 +3266,7 @@
         <v>60000</v>
       </c>
       <c r="G82" s="8">
-        <f>IFERROR(IF(B82&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B82)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A82)*100+MONTH(A82)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A82)*100+MONTH(A82)))),0)),""),"")</f>
+        <f>IFERROR(IF(B82&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B82)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A82)*100+MONTH(A82)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A82)*100+MONTH(A82)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H82" s="2" t="n"/>
@@ -3230,7 +3294,7 @@
         <v>60000</v>
       </c>
       <c r="G83" s="8">
-        <f>IFERROR(IF(B83&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B83)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A83)*100+MONTH(A83)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A83)*100+MONTH(A83)))),0)),""),"")</f>
+        <f>IFERROR(IF(B83&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B83)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A83)*100+MONTH(A83)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A83)*100+MONTH(A83)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H83" s="2" t="n"/>
@@ -3258,7 +3322,7 @@
         <v>60000</v>
       </c>
       <c r="G84" s="8">
-        <f>IFERROR(IF(B84&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B84)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A84)*100+MONTH(A84)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A84)*100+MONTH(A84)))),0)),""),"")</f>
+        <f>IFERROR(IF(B84&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B84)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A84)*100+MONTH(A84)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A84)*100+MONTH(A84)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H84" s="2" t="n"/>
@@ -3286,7 +3350,7 @@
         <v>60000</v>
       </c>
       <c r="G85" s="8">
-        <f>IFERROR(IF(B85&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B85)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A85)*100+MONTH(A85)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A85)*100+MONTH(A85)))),0)),""),"")</f>
+        <f>IFERROR(IF(B85&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B85)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A85)*100+MONTH(A85)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A85)*100+MONTH(A85)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H85" s="2" t="n"/>
@@ -3314,7 +3378,7 @@
         <v>60000</v>
       </c>
       <c r="G86" s="8">
-        <f>IFERROR(IF(B86&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B86)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A86)*100+MONTH(A86)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A86)*100+MONTH(A86)))),0)),""),"")</f>
+        <f>IFERROR(IF(B86&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B86)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A86)*100+MONTH(A86)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A86)*100+MONTH(A86)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H86" s="2" t="n"/>
@@ -3342,7 +3406,7 @@
         <v>48000</v>
       </c>
       <c r="G87" s="8">
-        <f>IFERROR(IF(B87&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B87)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A87)*100+MONTH(A87)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A87)*100+MONTH(A87)))),0)),""),"")</f>
+        <f>IFERROR(IF(B87&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B87)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A87)*100+MONTH(A87)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A87)*100+MONTH(A87)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H87" s="2" t="n"/>
@@ -3370,7 +3434,7 @@
         <v>60000</v>
       </c>
       <c r="G88" s="8">
-        <f>IFERROR(IF(B88&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B88)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A88)*100+MONTH(A88)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A88)*100+MONTH(A88)))),0)),""),"")</f>
+        <f>IFERROR(IF(B88&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B88)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A88)*100+MONTH(A88)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A88)*100+MONTH(A88)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H88" s="2" t="n"/>
@@ -3398,7 +3462,7 @@
         <v>60000</v>
       </c>
       <c r="G89" s="8">
-        <f>IFERROR(IF(B89&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B89)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A89)*100+MONTH(A89)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A89)*100+MONTH(A89)))),0)),""),"")</f>
+        <f>IFERROR(IF(B89&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B89)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A89)*100+MONTH(A89)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A89)*100+MONTH(A89)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H89" s="2" t="n"/>
@@ -3426,7 +3490,7 @@
         <v>60000</v>
       </c>
       <c r="G90" s="8">
-        <f>IFERROR(IF(B90&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B90)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A90)*100+MONTH(A90)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A90)*100+MONTH(A90)))),0)),""),"")</f>
+        <f>IFERROR(IF(B90&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B90)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A90)*100+MONTH(A90)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A90)*100+MONTH(A90)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H90" s="2" t="n"/>
@@ -3454,7 +3518,7 @@
         <v>60000</v>
       </c>
       <c r="G91" s="8">
-        <f>IFERROR(IF(B91&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B91)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A91)*100+MONTH(A91)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A91)*100+MONTH(A91)))),0)),""),"")</f>
+        <f>IFERROR(IF(B91&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B91)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A91)*100+MONTH(A91)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A91)*100+MONTH(A91)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H91" s="2" t="n"/>
@@ -3482,7 +3546,7 @@
         <v>60000</v>
       </c>
       <c r="G92" s="8">
-        <f>IFERROR(IF(B92&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B92)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A92)*100+MONTH(A92)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A92)*100+MONTH(A92)))),0)),""),"")</f>
+        <f>IFERROR(IF(B92&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B92)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A92)*100+MONTH(A92)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A92)*100+MONTH(A92)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H92" s="2" t="n"/>
@@ -3510,7 +3574,7 @@
         <v>48000</v>
       </c>
       <c r="G93" s="8">
-        <f>IFERROR(IF(B93&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B93)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A93)*100+MONTH(A93)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A93)*100+MONTH(A93)))),0)),""),"")</f>
+        <f>IFERROR(IF(B93&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B93)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A93)*100+MONTH(A93)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A93)*100+MONTH(A93)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H93" s="2" t="n"/>
@@ -3538,7 +3602,7 @@
         <v>60000</v>
       </c>
       <c r="G94" s="8">
-        <f>IFERROR(IF(B94&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B94)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A94)*100+MONTH(A94)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A94)*100+MONTH(A94)))),0)),""),"")</f>
+        <f>IFERROR(IF(B94&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B94)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A94)*100+MONTH(A94)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A94)*100+MONTH(A94)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H94" s="2" t="n"/>
@@ -3566,7 +3630,7 @@
         <v>60000</v>
       </c>
       <c r="G95" s="8">
-        <f>IFERROR(IF(B95&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B95)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A95)*100+MONTH(A95)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A95)*100+MONTH(A95)))),0)),""),"")</f>
+        <f>IFERROR(IF(B95&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B95)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A95)*100+MONTH(A95)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A95)*100+MONTH(A95)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H95" s="2" t="n"/>
@@ -3594,7 +3658,7 @@
         <v>60000</v>
       </c>
       <c r="G96" s="8">
-        <f>IFERROR(IF(B96&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B96)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A96)*100+MONTH(A96)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A96)*100+MONTH(A96)))),0)),""),"")</f>
+        <f>IFERROR(IF(B96&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B96)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A96)*100+MONTH(A96)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A96)*100+MONTH(A96)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H96" s="2" t="n"/>
@@ -3622,7 +3686,7 @@
         <v>60000</v>
       </c>
       <c r="G97" s="8">
-        <f>IFERROR(IF(B97&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B97)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A97)*100+MONTH(A97)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A97)*100+MONTH(A97)))),0)),""),"")</f>
+        <f>IFERROR(IF(B97&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B97)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A97)*100+MONTH(A97)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A97)*100+MONTH(A97)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H97" s="2" t="n"/>
@@ -3650,7 +3714,7 @@
         <v>60000</v>
       </c>
       <c r="G98" s="8">
-        <f>IFERROR(IF(B98&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B98)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A98)*100+MONTH(A98)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A98)*100+MONTH(A98)))),0)),""),"")</f>
+        <f>IFERROR(IF(B98&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B98)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A98)*100+MONTH(A98)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A98)*100+MONTH(A98)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H98" s="2" t="n"/>
@@ -3678,7 +3742,7 @@
         <v>48000</v>
       </c>
       <c r="G99" s="8">
-        <f>IFERROR(IF(B99&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B99)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A99)*100+MONTH(A99)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A99)*100+MONTH(A99)))),0)),""),"")</f>
+        <f>IFERROR(IF(B99&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B99)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A99)*100+MONTH(A99)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A99)*100+MONTH(A99)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H99" s="2" t="n"/>
@@ -3706,7 +3770,7 @@
         <v>60000</v>
       </c>
       <c r="G100" s="8">
-        <f>IFERROR(IF(B100&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B100)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A100)*100+MONTH(A100)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A100)*100+MONTH(A100)))),0)),""),"")</f>
+        <f>IFERROR(IF(B100&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B100)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A100)*100+MONTH(A100)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A100)*100+MONTH(A100)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H100" s="2" t="n"/>
@@ -3734,7 +3798,7 @@
         <v>60000</v>
       </c>
       <c r="G101" s="8">
-        <f>IFERROR(IF(B101&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B101)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A101)*100+MONTH(A101)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A101)*100+MONTH(A101)))),0)),""),"")</f>
+        <f>IFERROR(IF(B101&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B101)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A101)*100+MONTH(A101)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A101)*100+MONTH(A101)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H101" s="2" t="n"/>
@@ -3762,7 +3826,7 @@
         <v>60000</v>
       </c>
       <c r="G102" s="8">
-        <f>IFERROR(IF(B102&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B102)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A102)*100+MONTH(A102)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A102)*100+MONTH(A102)))),0)),""),"")</f>
+        <f>IFERROR(IF(B102&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B102)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A102)*100+MONTH(A102)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A102)*100+MONTH(A102)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H102" s="2" t="n"/>
@@ -3790,7 +3854,7 @@
         <v>48000</v>
       </c>
       <c r="G103" s="8">
-        <f>IFERROR(IF(B103&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B103)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A103)*100+MONTH(A103)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A103)*100+MONTH(A103)))),0)),""),"")</f>
+        <f>IFERROR(IF(B103&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B103)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A103)*100+MONTH(A103)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A103)*100+MONTH(A103)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H103" s="2" t="n"/>
@@ -3818,7 +3882,7 @@
         <v>60000</v>
       </c>
       <c r="G104" s="8">
-        <f>IFERROR(IF(B104&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B104)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A104)*100+MONTH(A104)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A104)*100+MONTH(A104)))),0)),""),"")</f>
+        <f>IFERROR(IF(B104&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B104)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A104)*100+MONTH(A104)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A104)*100+MONTH(A104)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H104" s="2" t="n"/>
@@ -3846,7 +3910,7 @@
         <v>60000</v>
       </c>
       <c r="G105" s="8">
-        <f>IFERROR(IF(B105&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B105)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A105)*100+MONTH(A105)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A105)*100+MONTH(A105)))),0)),""),"")</f>
+        <f>IFERROR(IF(B105&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B105)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A105)*100+MONTH(A105)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A105)*100+MONTH(A105)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H105" s="2" t="n"/>
@@ -3874,7 +3938,7 @@
         <v>60000</v>
       </c>
       <c r="G106" s="8">
-        <f>IFERROR(IF(B106&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B106)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A106)*100+MONTH(A106)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A106)*100+MONTH(A106)))),0)),""),"")</f>
+        <f>IFERROR(IF(B106&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B106)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A106)*100+MONTH(A106)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A106)*100+MONTH(A106)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H106" s="2" t="n"/>
@@ -3902,7 +3966,7 @@
         <v>60000</v>
       </c>
       <c r="G107" s="8">
-        <f>IFERROR(IF(B107&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B107)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A107)*100+MONTH(A107)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A107)*100+MONTH(A107)))),0)),""),"")</f>
+        <f>IFERROR(IF(B107&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B107)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A107)*100+MONTH(A107)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A107)*100+MONTH(A107)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H107" s="2" t="n"/>
@@ -3930,7 +3994,7 @@
         <v>60000</v>
       </c>
       <c r="G108" s="8">
-        <f>IFERROR(IF(B108&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B108)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A108)*100+MONTH(A108)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A108)*100+MONTH(A108)))),0)),""),"")</f>
+        <f>IFERROR(IF(B108&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B108)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A108)*100+MONTH(A108)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A108)*100+MONTH(A108)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H108" s="2" t="n"/>
@@ -3958,7 +4022,7 @@
         <v>48000</v>
       </c>
       <c r="G109" s="8">
-        <f>IFERROR(IF(B109&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B109)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A109)*100+MONTH(A109)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A109)*100+MONTH(A109)))),0)),""),"")</f>
+        <f>IFERROR(IF(B109&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B109)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A109)*100+MONTH(A109)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A109)*100+MONTH(A109)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H109" s="2" t="n"/>
@@ -3986,7 +4050,7 @@
         <v>60000</v>
       </c>
       <c r="G110" s="8">
-        <f>IFERROR(IF(B110&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B110)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A110)*100+MONTH(A110)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A110)*100+MONTH(A110)))),0)),""),"")</f>
+        <f>IFERROR(IF(B110&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B110)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A110)*100+MONTH(A110)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A110)*100+MONTH(A110)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H110" s="2" t="n"/>
@@ -4014,7 +4078,7 @@
         <v>60000</v>
       </c>
       <c r="G111" s="8">
-        <f>IFERROR(IF(B111&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B111)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A111)*100+MONTH(A111)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A111)*100+MONTH(A111)))),0)),""),"")</f>
+        <f>IFERROR(IF(B111&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B111)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A111)*100+MONTH(A111)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A111)*100+MONTH(A111)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H111" s="2" t="n"/>
@@ -4042,7 +4106,7 @@
         <v>60000</v>
       </c>
       <c r="G112" s="8">
-        <f>IFERROR(IF(B112&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B112)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A112)*100+MONTH(A112)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A112)*100+MONTH(A112)))),0)),""),"")</f>
+        <f>IFERROR(IF(B112&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B112)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A112)*100+MONTH(A112)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A112)*100+MONTH(A112)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H112" s="2" t="n"/>
@@ -4070,7 +4134,7 @@
         <v>60000</v>
       </c>
       <c r="G113" s="8">
-        <f>IFERROR(IF(B113&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B113)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A113)*100+MONTH(A113)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A113)*100+MONTH(A113)))),0)),""),"")</f>
+        <f>IFERROR(IF(B113&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B113)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A113)*100+MONTH(A113)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A113)*100+MONTH(A113)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H113" s="2" t="n"/>
@@ -4098,7 +4162,7 @@
         <v>60000</v>
       </c>
       <c r="G114" s="8">
-        <f>IFERROR(IF(B114&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B114)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A114)*100+MONTH(A114)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A114)*100+MONTH(A114)))),0)),""),"")</f>
+        <f>IFERROR(IF(B114&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B114)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A114)*100+MONTH(A114)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A114)*100+MONTH(A114)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H114" s="2" t="n"/>
@@ -4126,7 +4190,7 @@
         <v>48000</v>
       </c>
       <c r="G115" s="8">
-        <f>IFERROR(IF(B115&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B115)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A115)*100+MONTH(A115)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A115)*100+MONTH(A115)))),0)),""),"")</f>
+        <f>IFERROR(IF(B115&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B115)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A115)*100+MONTH(A115)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A115)*100+MONTH(A115)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H115" s="2" t="n"/>
@@ -4154,7 +4218,7 @@
         <v>60000</v>
       </c>
       <c r="G116" s="8">
-        <f>IFERROR(IF(B116&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B116)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A116)*100+MONTH(A116)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A116)*100+MONTH(A116)))),0)),""),"")</f>
+        <f>IFERROR(IF(B116&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B116)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A116)*100+MONTH(A116)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A116)*100+MONTH(A116)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H116" s="2" t="n"/>
@@ -4182,7 +4246,7 @@
         <v>60000</v>
       </c>
       <c r="G117" s="8">
-        <f>IFERROR(IF(B117&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B117)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A117)*100+MONTH(A117)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A117)*100+MONTH(A117)))),0)),""),"")</f>
+        <f>IFERROR(IF(B117&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B117)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A117)*100+MONTH(A117)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A117)*100+MONTH(A117)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H117" s="2" t="n"/>
@@ -4210,7 +4274,7 @@
         <v>60000</v>
       </c>
       <c r="G118" s="8">
-        <f>IFERROR(IF(B118&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B118)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A118)*100+MONTH(A118)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A118)*100+MONTH(A118)))),0)),""),"")</f>
+        <f>IFERROR(IF(B118&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B118)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A118)*100+MONTH(A118)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A118)*100+MONTH(A118)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H118" s="2" t="n"/>
@@ -4238,7 +4302,7 @@
         <v>60000</v>
       </c>
       <c r="G119" s="8">
-        <f>IFERROR(IF(B119&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B119)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A119)*100+MONTH(A119)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A119)*100+MONTH(A119)))),0)),""),"")</f>
+        <f>IFERROR(IF(B119&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B119)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A119)*100+MONTH(A119)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A119)*100+MONTH(A119)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H119" s="2" t="n"/>
@@ -4266,7 +4330,7 @@
         <v>60000</v>
       </c>
       <c r="G120" s="8">
-        <f>IFERROR(IF(B120&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B120)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A120)*100+MONTH(A120)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A120)*100+MONTH(A120)))),0)),""),"")</f>
+        <f>IFERROR(IF(B120&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B120)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A120)*100+MONTH(A120)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A120)*100+MONTH(A120)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H120" s="2" t="n"/>
@@ -4294,7 +4358,7 @@
         <v>48000</v>
       </c>
       <c r="G121" s="8">
-        <f>IFERROR(IF(B121&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B121)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A121)*100+MONTH(A121)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A121)*100+MONTH(A121)))),0)),""),"")</f>
+        <f>IFERROR(IF(B121&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B121)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A121)*100+MONTH(A121)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A121)*100+MONTH(A121)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H121" s="2" t="n"/>
@@ -4322,7 +4386,7 @@
         <v>60000</v>
       </c>
       <c r="G122" s="8">
-        <f>IFERROR(IF(B122&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B122)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A122)*100+MONTH(A122)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A122)*100+MONTH(A122)))),0)),""),"")</f>
+        <f>IFERROR(IF(B122&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B122)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A122)*100+MONTH(A122)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A122)*100+MONTH(A122)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H122" s="2" t="n"/>
@@ -4350,7 +4414,7 @@
         <v>60000</v>
       </c>
       <c r="G123" s="8">
-        <f>IFERROR(IF(B123&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B123)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A123)*100+MONTH(A123)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A123)*100+MONTH(A123)))),0)),""),"")</f>
+        <f>IFERROR(IF(B123&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B123)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A123)*100+MONTH(A123)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A123)*100+MONTH(A123)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H123" s="2" t="n"/>
@@ -4378,7 +4442,7 @@
         <v>60000</v>
       </c>
       <c r="G124" s="8">
-        <f>IFERROR(IF(B124&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B124)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A124)*100+MONTH(A124)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A124)*100+MONTH(A124)))),0)),""),"")</f>
+        <f>IFERROR(IF(B124&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B124)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A124)*100+MONTH(A124)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A124)*100+MONTH(A124)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H124" s="2" t="n"/>
@@ -4406,7 +4470,7 @@
         <v>60000</v>
       </c>
       <c r="G125" s="8">
-        <f>IFERROR(IF(B125&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B125)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A125)*100+MONTH(A125)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A125)*100+MONTH(A125)))),0)),""),"")</f>
+        <f>IFERROR(IF(B125&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B125)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A125)*100+MONTH(A125)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A125)*100+MONTH(A125)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H125" s="2" t="n"/>
@@ -4434,7 +4498,7 @@
         <v>60000</v>
       </c>
       <c r="G126" s="8">
-        <f>IFERROR(IF(B126&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B126)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A126)*100+MONTH(A126)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A126)*100+MONTH(A126)))),0)),""),"")</f>
+        <f>IFERROR(IF(B126&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B126)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A126)*100+MONTH(A126)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A126)*100+MONTH(A126)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H126" s="2" t="n"/>
@@ -4462,7 +4526,7 @@
         <v>48000</v>
       </c>
       <c r="G127" s="8">
-        <f>IFERROR(IF(B127&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B127)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A127)*100+MONTH(A127)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A127)*100+MONTH(A127)))),0)),""),"")</f>
+        <f>IFERROR(IF(B127&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B127)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A127)*100+MONTH(A127)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A127)*100+MONTH(A127)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H127" s="2" t="n"/>
@@ -4490,7 +4554,7 @@
         <v>60000</v>
       </c>
       <c r="G128" s="8">
-        <f>IFERROR(IF(B128&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B128)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A128)*100+MONTH(A128)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A128)*100+MONTH(A128)))),0)),""),"")</f>
+        <f>IFERROR(IF(B128&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B128)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A128)*100+MONTH(A128)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A128)*100+MONTH(A128)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H128" s="2" t="n"/>
@@ -4518,7 +4582,7 @@
         <v>60000</v>
       </c>
       <c r="G129" s="8">
-        <f>IFERROR(IF(B129&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B129)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A129)*100+MONTH(A129)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A129)*100+MONTH(A129)))),0)),""),"")</f>
+        <f>IFERROR(IF(B129&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B129)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A129)*100+MONTH(A129)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A129)*100+MONTH(A129)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H129" s="2" t="n"/>
@@ -4546,7 +4610,7 @@
         <v>60000</v>
       </c>
       <c r="G130" s="8">
-        <f>IFERROR(IF(B130&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B130)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A130)*100+MONTH(A130)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A130)*100+MONTH(A130)))),0)),""),"")</f>
+        <f>IFERROR(IF(B130&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B130)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A130)*100+MONTH(A130)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A130)*100+MONTH(A130)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H130" s="2" t="n"/>
@@ -4574,7 +4638,7 @@
         <v>60000</v>
       </c>
       <c r="G131" s="8">
-        <f>IFERROR(IF(B131&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B131)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A131)*100+MONTH(A131)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A131)*100+MONTH(A131)))),0)),""),"")</f>
+        <f>IFERROR(IF(B131&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B131)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A131)*100+MONTH(A131)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A131)*100+MONTH(A131)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H131" s="2" t="n"/>
@@ -4602,7 +4666,7 @@
         <v>60000</v>
       </c>
       <c r="G132" s="8">
-        <f>IFERROR(IF(B132&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B132)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A132)*100+MONTH(A132)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A132)*100+MONTH(A132)))),0)),""),"")</f>
+        <f>IFERROR(IF(B132&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B132)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A132)*100+MONTH(A132)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A132)*100+MONTH(A132)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H132" s="2" t="n"/>
@@ -4630,7 +4694,7 @@
         <v>48000</v>
       </c>
       <c r="G133" s="8">
-        <f>IFERROR(IF(B133&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B133)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A133)*100+MONTH(A133)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A133)*100+MONTH(A133)))),0)),""),"")</f>
+        <f>IFERROR(IF(B133&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B133)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A133)*100+MONTH(A133)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A133)*100+MONTH(A133)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H133" s="2" t="n"/>
@@ -4658,7 +4722,7 @@
         <v>60000</v>
       </c>
       <c r="G134" s="8">
-        <f>IFERROR(IF(B134&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B134)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A134)*100+MONTH(A134)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A134)*100+MONTH(A134)))),0)),""),"")</f>
+        <f>IFERROR(IF(B134&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B134)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A134)*100+MONTH(A134)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A134)*100+MONTH(A134)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H134" s="2" t="n"/>
@@ -4686,7 +4750,7 @@
         <v>60000</v>
       </c>
       <c r="G135" s="8">
-        <f>IFERROR(IF(B135&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B135)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A135)*100+MONTH(A135)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A135)*100+MONTH(A135)))),0)),""),"")</f>
+        <f>IFERROR(IF(B135&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B135)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A135)*100+MONTH(A135)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A135)*100+MONTH(A135)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H135" s="2" t="n"/>
@@ -4714,7 +4778,7 @@
         <v>60000</v>
       </c>
       <c r="G136" s="8">
-        <f>IFERROR(IF(B136&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B136)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A136)*100+MONTH(A136)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A136)*100+MONTH(A136)))),0)),""),"")</f>
+        <f>IFERROR(IF(B136&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B136)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A136)*100+MONTH(A136)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A136)*100+MONTH(A136)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H136" s="2" t="n"/>
@@ -4742,7 +4806,7 @@
         <v>60000</v>
       </c>
       <c r="G137" s="8">
-        <f>IFERROR(IF(B137&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B137)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A137)*100+MONTH(A137)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A137)*100+MONTH(A137)))),0)),""),"")</f>
+        <f>IFERROR(IF(B137&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B137)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A137)*100+MONTH(A137)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A137)*100+MONTH(A137)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H137" s="2" t="n"/>
@@ -4770,7 +4834,7 @@
         <v>60000</v>
       </c>
       <c r="G138" s="8">
-        <f>IFERROR(IF(B138&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B138)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A138)*100+MONTH(A138)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A138)*100+MONTH(A138)))),0)),""),"")</f>
+        <f>IFERROR(IF(B138&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B138)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A138)*100+MONTH(A138)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A138)*100+MONTH(A138)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H138" s="2" t="n"/>
@@ -4798,7 +4862,7 @@
         <v>48000</v>
       </c>
       <c r="G139" s="8">
-        <f>IFERROR(IF(B139&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B139)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A139)*100+MONTH(A139)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A139)*100+MONTH(A139)))),0)),""),"")</f>
+        <f>IFERROR(IF(B139&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B139)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A139)*100+MONTH(A139)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A139)*100+MONTH(A139)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H139" s="2" t="n"/>
@@ -4826,7 +4890,7 @@
         <v>48000</v>
       </c>
       <c r="G140" s="8">
-        <f>IFERROR(IF(B140&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B140)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A140)*100+MONTH(A140)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A140)*100+MONTH(A140)))),0)),""),"")</f>
+        <f>IFERROR(IF(B140&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B140)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A140)*100+MONTH(A140)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A140)*100+MONTH(A140)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H140" s="2" t="n"/>
@@ -4854,7 +4918,7 @@
         <v>48000</v>
       </c>
       <c r="G141" s="8">
-        <f>IFERROR(IF(B141&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B141)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A141)*100+MONTH(A141)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A141)*100+MONTH(A141)))),0)),""),"")</f>
+        <f>IFERROR(IF(B141&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B141)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A141)*100+MONTH(A141)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A141)*100+MONTH(A141)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H141" s="2" t="n"/>
@@ -4882,7 +4946,7 @@
         <v>48000</v>
       </c>
       <c r="G142" s="8">
-        <f>IFERROR(IF(B142&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B142)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A142)*100+MONTH(A142)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A142)*100+MONTH(A142)))),0)),""),"")</f>
+        <f>IFERROR(IF(B142&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B142)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A142)*100+MONTH(A142)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A142)*100+MONTH(A142)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H142" s="2" t="n"/>
@@ -4910,7 +4974,7 @@
         <v>60000</v>
       </c>
       <c r="G143" s="8">
-        <f>IFERROR(IF(B143&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B143)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A143)*100+MONTH(A143)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A143)*100+MONTH(A143)))),0)),""),"")</f>
+        <f>IFERROR(IF(B143&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B143)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A143)*100+MONTH(A143)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A143)*100+MONTH(A143)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H143" s="2" t="n"/>
@@ -4938,7 +5002,7 @@
         <v>60000</v>
       </c>
       <c r="G144" s="8">
-        <f>IFERROR(IF(B144&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B144)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A144)*100+MONTH(A144)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A144)*100+MONTH(A144)))),0)),""),"")</f>
+        <f>IFERROR(IF(B144&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B144)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A144)*100+MONTH(A144)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A144)*100+MONTH(A144)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H144" s="2" t="n"/>
@@ -4966,7 +5030,7 @@
         <v>48000</v>
       </c>
       <c r="G145" s="8">
-        <f>IFERROR(IF(B145&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B145)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A145)*100+MONTH(A145)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A145)*100+MONTH(A145)))),0)),""),"")</f>
+        <f>IFERROR(IF(B145&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B145)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A145)*100+MONTH(A145)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A145)*100+MONTH(A145)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H145" s="2" t="n"/>
@@ -4994,7 +5058,7 @@
         <v>48000</v>
       </c>
       <c r="G146" s="8">
-        <f>IFERROR(IF(B146&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B146)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A146)*100+MONTH(A146)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A146)*100+MONTH(A146)))),0)),""),"")</f>
+        <f>IFERROR(IF(B146&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B146)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A146)*100+MONTH(A146)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A146)*100+MONTH(A146)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H146" s="2" t="n"/>
@@ -5022,7 +5086,7 @@
         <v>48000</v>
       </c>
       <c r="G147" s="8">
-        <f>IFERROR(IF(B147&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B147)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A147)*100+MONTH(A147)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A147)*100+MONTH(A147)))),0)),""),"")</f>
+        <f>IFERROR(IF(B147&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B147)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A147)*100+MONTH(A147)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A147)*100+MONTH(A147)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H147" s="2" t="n"/>
@@ -5050,7 +5114,7 @@
         <v>48000</v>
       </c>
       <c r="G148" s="8">
-        <f>IFERROR(IF(B148&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B148)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A148)*100+MONTH(A148)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A148)*100+MONTH(A148)))),0)),""),"")</f>
+        <f>IFERROR(IF(B148&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B148)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A148)*100+MONTH(A148)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A148)*100+MONTH(A148)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H148" s="2" t="n"/>
@@ -5078,7 +5142,7 @@
         <v>60000</v>
       </c>
       <c r="G149" s="8">
-        <f>IFERROR(IF(B149&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B149)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A149)*100+MONTH(A149)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A149)*100+MONTH(A149)))),0)),""),"")</f>
+        <f>IFERROR(IF(B149&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B149)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A149)*100+MONTH(A149)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A149)*100+MONTH(A149)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H149" s="2" t="n"/>
@@ -5106,7 +5170,7 @@
         <v>60000</v>
       </c>
       <c r="G150" s="8">
-        <f>IFERROR(IF(B150&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B150)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A150)*100+MONTH(A150)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A150)*100+MONTH(A150)))),0)),""),"")</f>
+        <f>IFERROR(IF(B150&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B150)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A150)*100+MONTH(A150)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A150)*100+MONTH(A150)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H150" s="2" t="n"/>
@@ -5134,7 +5198,7 @@
         <v>48000</v>
       </c>
       <c r="G151" s="8">
-        <f>IFERROR(IF(B151&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B151)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A151)*100+MONTH(A151)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A151)*100+MONTH(A151)))),0)),""),"")</f>
+        <f>IFERROR(IF(B151&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B151)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A151)*100+MONTH(A151)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A151)*100+MONTH(A151)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H151" s="2" t="n"/>
@@ -5162,7 +5226,7 @@
         <v>48000</v>
       </c>
       <c r="G152" s="8">
-        <f>IFERROR(IF(B152&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B152)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A152)*100+MONTH(A152)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A152)*100+MONTH(A152)))),0)),""),"")</f>
+        <f>IFERROR(IF(B152&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B152)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A152)*100+MONTH(A152)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A152)*100+MONTH(A152)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H152" s="2" t="n"/>
@@ -5190,7 +5254,7 @@
         <v>48000</v>
       </c>
       <c r="G153" s="8">
-        <f>IFERROR(IF(B153&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B153)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A153)*100+MONTH(A153)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A153)*100+MONTH(A153)))),0)),""),"")</f>
+        <f>IFERROR(IF(B153&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B153)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A153)*100+MONTH(A153)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A153)*100+MONTH(A153)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H153" s="2" t="n"/>
@@ -5218,7 +5282,7 @@
         <v>48000</v>
       </c>
       <c r="G154" s="8">
-        <f>IFERROR(IF(B154&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B154)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A154)*100+MONTH(A154)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A154)*100+MONTH(A154)))),0)),""),"")</f>
+        <f>IFERROR(IF(B154&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B154)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A154)*100+MONTH(A154)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A154)*100+MONTH(A154)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H154" s="2" t="n"/>
@@ -5246,7 +5310,7 @@
         <v>60000</v>
       </c>
       <c r="G155" s="8">
-        <f>IFERROR(IF(B155&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B155)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A155)*100+MONTH(A155)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A155)*100+MONTH(A155)))),0)),""),"")</f>
+        <f>IFERROR(IF(B155&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B155)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A155)*100+MONTH(A155)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A155)*100+MONTH(A155)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H155" s="2" t="n"/>
@@ -5274,7 +5338,7 @@
         <v>60000</v>
       </c>
       <c r="G156" s="8">
-        <f>IFERROR(IF(B156&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B156)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A156)*100+MONTH(A156)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A156)*100+MONTH(A156)))),0)),""),"")</f>
+        <f>IFERROR(IF(B156&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B156)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A156)*100+MONTH(A156)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A156)*100+MONTH(A156)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H156" s="2" t="n"/>
@@ -5302,7 +5366,7 @@
         <v>48000</v>
       </c>
       <c r="G157" s="8">
-        <f>IFERROR(IF(B157&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B157)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A157)*100+MONTH(A157)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A157)*100+MONTH(A157)))),0)),""),"")</f>
+        <f>IFERROR(IF(B157&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B157)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A157)*100+MONTH(A157)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A157)*100+MONTH(A157)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H157" s="2" t="n"/>
@@ -5330,7 +5394,7 @@
         <v>48000</v>
       </c>
       <c r="G158" s="8">
-        <f>IFERROR(IF(B158&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B158)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A158)*100+MONTH(A158)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A158)*100+MONTH(A158)))),0)),""),"")</f>
+        <f>IFERROR(IF(B158&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B158)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A158)*100+MONTH(A158)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A158)*100+MONTH(A158)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H158" s="2" t="n"/>
@@ -5358,7 +5422,7 @@
         <v>48000</v>
       </c>
       <c r="G159" s="8">
-        <f>IFERROR(IF(B159&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B159)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A159)*100+MONTH(A159)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A159)*100+MONTH(A159)))),0)),""),"")</f>
+        <f>IFERROR(IF(B159&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B159)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A159)*100+MONTH(A159)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A159)*100+MONTH(A159)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H159" s="2" t="n"/>
@@ -5386,7 +5450,7 @@
         <v>48000</v>
       </c>
       <c r="G160" s="8">
-        <f>IFERROR(IF(B160&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B160)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A160)*100+MONTH(A160)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A160)*100+MONTH(A160)))),0)),""),"")</f>
+        <f>IFERROR(IF(B160&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B160)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A160)*100+MONTH(A160)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A160)*100+MONTH(A160)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H160" s="2" t="n"/>
@@ -5414,7 +5478,7 @@
         <v>60000</v>
       </c>
       <c r="G161" s="8">
-        <f>IFERROR(IF(B161&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B161)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A161)*100+MONTH(A161)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A161)*100+MONTH(A161)))),0)),""),"")</f>
+        <f>IFERROR(IF(B161&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B161)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A161)*100+MONTH(A161)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A161)*100+MONTH(A161)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H161" s="2" t="n"/>
@@ -5442,7 +5506,7 @@
         <v>48000</v>
       </c>
       <c r="G162" s="8">
-        <f>IFERROR(IF(B162&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B162)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A162)*100+MONTH(A162)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A162)*100+MONTH(A162)))),0)),""),"")</f>
+        <f>IFERROR(IF(B162&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B162)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A162)*100+MONTH(A162)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A162)*100+MONTH(A162)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H162" s="2" t="n"/>
@@ -5470,7 +5534,7 @@
         <v>48000</v>
       </c>
       <c r="G163" s="8">
-        <f>IFERROR(IF(B163&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B163)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A163)*100+MONTH(A163)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A163)*100+MONTH(A163)))),0)),""),"")</f>
+        <f>IFERROR(IF(B163&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B163)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A163)*100+MONTH(A163)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A163)*100+MONTH(A163)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H163" s="2" t="n"/>
@@ -5498,7 +5562,7 @@
         <v>48000</v>
       </c>
       <c r="G164" s="8">
-        <f>IFERROR(IF(B164&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B164)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A164)*100+MONTH(A164)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A164)*100+MONTH(A164)))),0)),""),"")</f>
+        <f>IFERROR(IF(B164&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B164)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A164)*100+MONTH(A164)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A164)*100+MONTH(A164)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H164" s="2" t="n"/>
@@ -5526,7 +5590,7 @@
         <v>48000</v>
       </c>
       <c r="G165" s="8">
-        <f>IFERROR(IF(B165&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B165)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A165)*100+MONTH(A165)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A165)*100+MONTH(A165)))),0)),""),"")</f>
+        <f>IFERROR(IF(B165&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B165)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A165)*100+MONTH(A165)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A165)*100+MONTH(A165)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H165" s="2" t="n"/>
@@ -5554,7 +5618,7 @@
         <v>60000</v>
       </c>
       <c r="G166" s="8">
-        <f>IFERROR(IF(B166&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B166)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A166)*100+MONTH(A166)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A166)*100+MONTH(A166)))),0)),""),"")</f>
+        <f>IFERROR(IF(B166&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B166)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A166)*100+MONTH(A166)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A166)*100+MONTH(A166)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H166" s="2" t="n"/>
@@ -5582,7 +5646,7 @@
         <v>60000</v>
       </c>
       <c r="G167" s="8">
-        <f>IFERROR(IF(B167&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B167)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A167)*100+MONTH(A167)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A167)*100+MONTH(A167)))),0)),""),"")</f>
+        <f>IFERROR(IF(B167&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B167)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A167)*100+MONTH(A167)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A167)*100+MONTH(A167)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H167" s="2" t="n"/>
@@ -5610,7 +5674,7 @@
         <v>48000</v>
       </c>
       <c r="G168" s="8">
-        <f>IFERROR(IF(B168&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B168)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A168)*100+MONTH(A168)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A168)*100+MONTH(A168)))),0)),""),"")</f>
+        <f>IFERROR(IF(B168&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B168)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A168)*100+MONTH(A168)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A168)*100+MONTH(A168)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H168" s="2" t="n"/>
@@ -5638,7 +5702,7 @@
         <v>48000</v>
       </c>
       <c r="G169" s="8">
-        <f>IFERROR(IF(B169&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B169)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A169)*100+MONTH(A169)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A169)*100+MONTH(A169)))),0)),""),"")</f>
+        <f>IFERROR(IF(B169&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B169)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A169)*100+MONTH(A169)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A169)*100+MONTH(A169)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H169" s="2" t="n"/>
@@ -5666,7 +5730,7 @@
         <v>48000</v>
       </c>
       <c r="G170" s="8">
-        <f>IFERROR(IF(B170&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B170)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A170)*100+MONTH(A170)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A170)*100+MONTH(A170)))),0)),""),"")</f>
+        <f>IFERROR(IF(B170&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B170)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A170)*100+MONTH(A170)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A170)*100+MONTH(A170)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H170" s="2" t="n"/>
@@ -5694,7 +5758,7 @@
         <v>48000</v>
       </c>
       <c r="G171" s="8">
-        <f>IFERROR(IF(B171&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B171)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A171)*100+MONTH(A171)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A171)*100+MONTH(A171)))),0)),""),"")</f>
+        <f>IFERROR(IF(B171&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B171)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A171)*100+MONTH(A171)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A171)*100+MONTH(A171)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H171" s="2" t="n"/>
@@ -5722,7 +5786,7 @@
         <v>60000</v>
       </c>
       <c r="G172" s="8">
-        <f>IFERROR(IF(B172&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B172)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A172)*100+MONTH(A172)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A172)*100+MONTH(A172)))),0)),""),"")</f>
+        <f>IFERROR(IF(B172&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B172)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A172)*100+MONTH(A172)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A172)*100+MONTH(A172)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H172" s="2" t="n"/>
@@ -5750,7 +5814,7 @@
         <v>60000</v>
       </c>
       <c r="G173" s="8">
-        <f>IFERROR(IF(B173&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B173)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A173)*100+MONTH(A173)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A173)*100+MONTH(A173)))),0)),""),"")</f>
+        <f>IFERROR(IF(B173&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B173)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A173)*100+MONTH(A173)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A173)*100+MONTH(A173)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H173" s="2" t="n"/>
@@ -5778,7 +5842,7 @@
         <v>48000</v>
       </c>
       <c r="G174" s="8">
-        <f>IFERROR(IF(B174&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B174)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A174)*100+MONTH(A174)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A174)*100+MONTH(A174)))),0)),""),"")</f>
+        <f>IFERROR(IF(B174&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B174)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A174)*100+MONTH(A174)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A174)*100+MONTH(A174)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H174" s="2" t="n"/>
@@ -5806,7 +5870,7 @@
         <v>48000</v>
       </c>
       <c r="G175" s="8">
-        <f>IFERROR(IF(B175&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B175)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A175)*100+MONTH(A175)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A175)*100+MONTH(A175)))),0)),""),"")</f>
+        <f>IFERROR(IF(B175&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B175)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A175)*100+MONTH(A175)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A175)*100+MONTH(A175)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H175" s="2" t="n"/>
@@ -5834,7 +5898,7 @@
         <v>48000</v>
       </c>
       <c r="G176" s="8">
-        <f>IFERROR(IF(B176&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B176)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A176)*100+MONTH(A176)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A176)*100+MONTH(A176)))),0)),""),"")</f>
+        <f>IFERROR(IF(B176&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B176)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A176)*100+MONTH(A176)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A176)*100+MONTH(A176)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H176" s="2" t="n"/>
@@ -5862,7 +5926,7 @@
         <v>48000</v>
       </c>
       <c r="G177" s="8">
-        <f>IFERROR(IF(B177&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B177)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A177)*100+MONTH(A177)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A177)*100+MONTH(A177)))),0)),""),"")</f>
+        <f>IFERROR(IF(B177&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B177)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A177)*100+MONTH(A177)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A177)*100+MONTH(A177)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H177" s="2" t="n"/>
@@ -5890,7 +5954,7 @@
         <v>48000</v>
       </c>
       <c r="G178" s="8">
-        <f>IFERROR(IF(B178&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B178)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A178)*100+MONTH(A178)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A178)*100+MONTH(A178)))),0)),""),"")</f>
+        <f>IFERROR(IF(B178&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B178)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A178)*100+MONTH(A178)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A178)*100+MONTH(A178)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H178" s="2" t="n"/>
@@ -5918,7 +5982,7 @@
         <v>48000</v>
       </c>
       <c r="G179" s="8">
-        <f>IFERROR(IF(B179&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B179)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A179)*100+MONTH(A179)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A179)*100+MONTH(A179)))),0)),""),"")</f>
+        <f>IFERROR(IF(B179&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B179)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A179)*100+MONTH(A179)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A179)*100+MONTH(A179)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H179" s="2" t="n"/>
@@ -5946,7 +6010,7 @@
         <v>48000</v>
       </c>
       <c r="G180" s="8">
-        <f>IFERROR(IF(B180&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B180)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A180)*100+MONTH(A180)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A180)*100+MONTH(A180)))),0)),""),"")</f>
+        <f>IFERROR(IF(B180&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B180)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A180)*100+MONTH(A180)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A180)*100+MONTH(A180)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H180" s="2" t="n"/>
@@ -5974,7 +6038,7 @@
         <v>48000</v>
       </c>
       <c r="G181" s="8">
-        <f>IFERROR(IF(B181&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B181)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A181)*100+MONTH(A181)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A181)*100+MONTH(A181)))),0)),""),"")</f>
+        <f>IFERROR(IF(B181&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B181)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A181)*100+MONTH(A181)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A181)*100+MONTH(A181)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H181" s="2" t="n"/>
@@ -6002,7 +6066,7 @@
         <v>48000</v>
       </c>
       <c r="G182" s="8">
-        <f>IFERROR(IF(B182&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B182)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A182)*100+MONTH(A182)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A182)*100+MONTH(A182)))),0)),""),"")</f>
+        <f>IFERROR(IF(B182&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B182)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A182)*100+MONTH(A182)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A182)*100+MONTH(A182)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H182" s="2" t="n"/>
@@ -6030,7 +6094,7 @@
         <v>48000</v>
       </c>
       <c r="G183" s="8">
-        <f>IFERROR(IF(B183&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B183)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A183)*100+MONTH(A183)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A183)*100+MONTH(A183)))),0)),""),"")</f>
+        <f>IFERROR(IF(B183&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B183)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A183)*100+MONTH(A183)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A183)*100+MONTH(A183)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H183" s="2" t="n"/>
@@ -6058,7 +6122,7 @@
         <v>48000</v>
       </c>
       <c r="G184" s="8">
-        <f>IFERROR(IF(B184&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B184)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A184)*100+MONTH(A184)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A184)*100+MONTH(A184)))),0)),""),"")</f>
+        <f>IFERROR(IF(B184&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B184)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A184)*100+MONTH(A184)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A184)*100+MONTH(A184)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H184" s="2" t="n"/>
@@ -6086,7 +6150,7 @@
         <v>48000</v>
       </c>
       <c r="G185" s="8">
-        <f>IFERROR(IF(B185&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B185)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A185)*100+MONTH(A185)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A185)*100+MONTH(A185)))),0)),""),"")</f>
+        <f>IFERROR(IF(B185&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B185)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A185)*100+MONTH(A185)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A185)*100+MONTH(A185)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H185" s="2" t="n"/>
@@ -6114,7 +6178,7 @@
         <v>48000</v>
       </c>
       <c r="G186" s="8">
-        <f>IFERROR(IF(B186&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B186)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A186)*100+MONTH(A186)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A186)*100+MONTH(A186)))),0)),""),"")</f>
+        <f>IFERROR(IF(B186&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B186)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A186)*100+MONTH(A186)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A186)*100+MONTH(A186)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H186" s="2" t="n"/>
@@ -6142,7 +6206,7 @@
         <v>48000</v>
       </c>
       <c r="G187" s="8">
-        <f>IFERROR(IF(B187&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B187)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A187)*100+MONTH(A187)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A187)*100+MONTH(A187)))),0)),""),"")</f>
+        <f>IFERROR(IF(B187&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B187)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A187)*100+MONTH(A187)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A187)*100+MONTH(A187)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H187" s="2" t="n"/>
@@ -6170,7 +6234,7 @@
         <v>48000</v>
       </c>
       <c r="G188" s="8">
-        <f>IFERROR(IF(B188&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B188)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A188)*100+MONTH(A188)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A188)*100+MONTH(A188)))),0)),""),"")</f>
+        <f>IFERROR(IF(B188&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B188)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A188)*100+MONTH(A188)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A188)*100+MONTH(A188)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H188" s="2" t="n"/>
@@ -6198,7 +6262,7 @@
         <v>48000</v>
       </c>
       <c r="G189" s="8">
-        <f>IFERROR(IF(B189&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B189)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A189)*100+MONTH(A189)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A189)*100+MONTH(A189)))),0)),""),"")</f>
+        <f>IFERROR(IF(B189&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B189)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A189)*100+MONTH(A189)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A189)*100+MONTH(A189)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H189" s="2" t="n"/>
@@ -6226,7 +6290,7 @@
         <v>48000</v>
       </c>
       <c r="G190" s="8">
-        <f>IFERROR(IF(B190&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B190)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A190)*100+MONTH(A190)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A190)*100+MONTH(A190)))),0)),""),"")</f>
+        <f>IFERROR(IF(B190&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B190)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A190)*100+MONTH(A190)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A190)*100+MONTH(A190)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H190" s="2" t="n"/>
@@ -6254,7 +6318,7 @@
         <v>48000</v>
       </c>
       <c r="G191" s="8">
-        <f>IFERROR(IF(B191&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B191)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A191)*100+MONTH(A191)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A191)*100+MONTH(A191)))),0)),""),"")</f>
+        <f>IFERROR(IF(B191&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B191)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A191)*100+MONTH(A191)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A191)*100+MONTH(A191)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H191" s="2" t="n"/>
@@ -6282,7 +6346,7 @@
         <v>48000</v>
       </c>
       <c r="G192" s="8">
-        <f>IFERROR(IF(B192&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B192)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A192)*100+MONTH(A192)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A192)*100+MONTH(A192)))),0)),""),"")</f>
+        <f>IFERROR(IF(B192&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B192)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A192)*100+MONTH(A192)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A192)*100+MONTH(A192)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H192" s="2" t="n"/>
@@ -6310,7 +6374,7 @@
         <v>48000</v>
       </c>
       <c r="G193" s="8">
-        <f>IFERROR(IF(B193&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B193)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A193)*100+MONTH(A193)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A193)*100+MONTH(A193)))),0)),""),"")</f>
+        <f>IFERROR(IF(B193&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B193)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A193)*100+MONTH(A193)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A193)*100+MONTH(A193)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H193" s="2" t="n"/>
@@ -6338,7 +6402,7 @@
         <v>48000</v>
       </c>
       <c r="G194" s="8">
-        <f>IFERROR(IF(B194&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B194)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A194)*100+MONTH(A194)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A194)*100+MONTH(A194)))),0)),""),"")</f>
+        <f>IFERROR(IF(B194&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B194)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A194)*100+MONTH(A194)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A194)*100+MONTH(A194)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H194" s="2" t="n"/>
@@ -6366,7 +6430,7 @@
         <v>48000</v>
       </c>
       <c r="G195" s="8">
-        <f>IFERROR(IF(B195&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B195)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A195)*100+MONTH(A195)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A195)*100+MONTH(A195)))),0)),""),"")</f>
+        <f>IFERROR(IF(B195&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B195)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A195)*100+MONTH(A195)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A195)*100+MONTH(A195)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H195" s="2" t="n"/>
@@ -6394,7 +6458,7 @@
         <v>48000</v>
       </c>
       <c r="G196" s="8">
-        <f>IFERROR(IF(B196&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B196)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A196)*100+MONTH(A196)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A196)*100+MONTH(A196)))),0)),""),"")</f>
+        <f>IFERROR(IF(B196&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B196)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A196)*100+MONTH(A196)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A196)*100+MONTH(A196)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H196" s="2" t="n"/>
@@ -6422,7 +6486,7 @@
         <v>48000</v>
       </c>
       <c r="G197" s="8">
-        <f>IFERROR(IF(B197&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B197)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A197)*100+MONTH(A197)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A197)*100+MONTH(A197)))),0)),""),"")</f>
+        <f>IFERROR(IF(B197&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B197)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A197)*100+MONTH(A197)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A197)*100+MONTH(A197)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H197" s="2" t="n"/>
@@ -6450,7 +6514,7 @@
         <v>48000</v>
       </c>
       <c r="G198" s="8">
-        <f>IFERROR(IF(B198&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B198)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A198)*100+MONTH(A198)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A198)*100+MONTH(A198)))),0)),""),"")</f>
+        <f>IFERROR(IF(B198&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B198)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A198)*100+MONTH(A198)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A198)*100+MONTH(A198)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H198" s="2" t="n"/>
@@ -6478,7 +6542,7 @@
         <v>48000</v>
       </c>
       <c r="G199" s="8">
-        <f>IFERROR(IF(B199&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B199)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A199)*100+MONTH(A199)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A199)*100+MONTH(A199)))),0)),""),"")</f>
+        <f>IFERROR(IF(B199&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B199)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A199)*100+MONTH(A199)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A199)*100+MONTH(A199)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H199" s="2" t="n"/>
@@ -6506,7 +6570,7 @@
         <v>48000</v>
       </c>
       <c r="G200" s="8">
-        <f>IFERROR(IF(B200&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B200)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A200)*100+MONTH(A200)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A200)*100+MONTH(A200)))),0)),""),"")</f>
+        <f>IFERROR(IF(B200&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B200)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A200)*100+MONTH(A200)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A200)*100+MONTH(A200)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H200" s="2" t="n"/>
@@ -6534,7 +6598,7 @@
         <v>48000</v>
       </c>
       <c r="G201" s="8">
-        <f>IFERROR(IF(B201&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B201)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A201)*100+MONTH(A201)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A201)*100+MONTH(A201)))),0)),""),"")</f>
+        <f>IFERROR(IF(B201&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B201)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A201)*100+MONTH(A201)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A201)*100+MONTH(A201)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H201" s="2" t="n"/>
@@ -6562,7 +6626,7 @@
         <v>48000</v>
       </c>
       <c r="G202" s="8">
-        <f>IFERROR(IF(B202&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B202)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A202)*100+MONTH(A202)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A202)*100+MONTH(A202)))),0)),""),"")</f>
+        <f>IFERROR(IF(B202&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B202)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A202)*100+MONTH(A202)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A202)*100+MONTH(A202)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H202" s="2" t="n"/>
@@ -6590,7 +6654,7 @@
         <v>48000</v>
       </c>
       <c r="G203" s="8">
-        <f>IFERROR(IF(B203&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B203)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A203)*100+MONTH(A203)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A203)*100+MONTH(A203)))),0)),""),"")</f>
+        <f>IFERROR(IF(B203&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B203)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A203)*100+MONTH(A203)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A203)*100+MONTH(A203)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H203" s="2" t="n"/>
@@ -6618,7 +6682,7 @@
         <v>54000</v>
       </c>
       <c r="G204" s="8">
-        <f>IFERROR(IF(B204&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B204)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A204)*100+MONTH(A204)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A204)*100+MONTH(A204)))),0)),""),"")</f>
+        <f>IFERROR(IF(B204&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B204)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A204)*100+MONTH(A204)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A204)*100+MONTH(A204)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H204" s="2" t="n"/>
@@ -6646,7 +6710,7 @@
         <v>48000</v>
       </c>
       <c r="G205" s="8">
-        <f>IFERROR(IF(B205&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B205)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A205)*100+MONTH(A205)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A205)*100+MONTH(A205)))),0)),""),"")</f>
+        <f>IFERROR(IF(B205&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B205)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A205)*100+MONTH(A205)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A205)*100+MONTH(A205)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H205" s="2" t="n"/>
@@ -6674,7 +6738,7 @@
         <v>48000</v>
       </c>
       <c r="G206" s="8">
-        <f>IFERROR(IF(B206&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B206)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A206)*100+MONTH(A206)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A206)*100+MONTH(A206)))),0)),""),"")</f>
+        <f>IFERROR(IF(B206&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B206)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A206)*100+MONTH(A206)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A206)*100+MONTH(A206)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H206" s="2" t="n"/>
@@ -6702,7 +6766,7 @@
         <v>48000</v>
       </c>
       <c r="G207" s="8">
-        <f>IFERROR(IF(B207&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B207)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A207)*100+MONTH(A207)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A207)*100+MONTH(A207)))),0)),""),"")</f>
+        <f>IFERROR(IF(B207&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B207)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A207)*100+MONTH(A207)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A207)*100+MONTH(A207)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H207" s="2" t="n"/>
@@ -6730,7 +6794,7 @@
         <v>48000</v>
       </c>
       <c r="G208" s="8">
-        <f>IFERROR(IF(B208&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B208)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A208)*100+MONTH(A208)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A208)*100+MONTH(A208)))),0)),""),"")</f>
+        <f>IFERROR(IF(B208&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B208)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A208)*100+MONTH(A208)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A208)*100+MONTH(A208)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H208" s="2" t="n"/>
@@ -6758,7 +6822,7 @@
         <v>48000</v>
       </c>
       <c r="G209" s="8">
-        <f>IFERROR(IF(B209&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B209)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A209)*100+MONTH(A209)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A209)*100+MONTH(A209)))),0)),""),"")</f>
+        <f>IFERROR(IF(B209&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B209)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A209)*100+MONTH(A209)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A209)*100+MONTH(A209)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H209" s="2" t="n"/>
@@ -6786,7 +6850,7 @@
         <v>48000</v>
       </c>
       <c r="G210" s="8">
-        <f>IFERROR(IF(B210&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B210)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A210)*100+MONTH(A210)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A210)*100+MONTH(A210)))),0)),""),"")</f>
+        <f>IFERROR(IF(B210&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B210)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A210)*100+MONTH(A210)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A210)*100+MONTH(A210)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H210" s="2" t="n"/>
@@ -6814,7 +6878,7 @@
         <v>48000</v>
       </c>
       <c r="G211" s="8">
-        <f>IFERROR(IF(B211&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B211)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A211)*100+MONTH(A211)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A211)*100+MONTH(A211)))),0)),""),"")</f>
+        <f>IFERROR(IF(B211&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B211)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A211)*100+MONTH(A211)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A211)*100+MONTH(A211)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H211" s="2" t="n"/>
@@ -6842,7 +6906,7 @@
         <v>48000</v>
       </c>
       <c r="G212" s="8">
-        <f>IFERROR(IF(B212&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B212)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A212)*100+MONTH(A212)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A212)*100+MONTH(A212)))),0)),""),"")</f>
+        <f>IFERROR(IF(B212&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B212)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A212)*100+MONTH(A212)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A212)*100+MONTH(A212)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H212" s="2" t="n"/>
@@ -6870,7 +6934,7 @@
         <v>84000</v>
       </c>
       <c r="G213" s="8">
-        <f>IFERROR(IF(B213&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B213)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A213)*100+MONTH(A213)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A213)*100+MONTH(A213)))),0)),""),"")</f>
+        <f>IFERROR(IF(B213&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B213)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A213)*100+MONTH(A213)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A213)*100+MONTH(A213)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H213" s="2" t="n"/>
@@ -6898,7 +6962,7 @@
         <v>48000</v>
       </c>
       <c r="G214" s="8">
-        <f>IFERROR(IF(B214&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B214)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A214)*100+MONTH(A214)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A214)*100+MONTH(A214)))),0)),""),"")</f>
+        <f>IFERROR(IF(B214&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B214)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A214)*100+MONTH(A214)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A214)*100+MONTH(A214)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H214" s="2" t="n"/>
@@ -6926,7 +6990,7 @@
         <v>48000</v>
       </c>
       <c r="G215" s="8">
-        <f>IFERROR(IF(B215&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B215)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A215)*100+MONTH(A215)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A215)*100+MONTH(A215)))),0)),""),"")</f>
+        <f>IFERROR(IF(B215&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B215)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A215)*100+MONTH(A215)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A215)*100+MONTH(A215)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H215" s="2" t="n"/>
@@ -6954,7 +7018,7 @@
         <v>48000</v>
       </c>
       <c r="G216" s="8">
-        <f>IFERROR(IF(B216&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B216)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A216)*100+MONTH(A216)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A216)*100+MONTH(A216)))),0)),""),"")</f>
+        <f>IFERROR(IF(B216&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B216)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A216)*100+MONTH(A216)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A216)*100+MONTH(A216)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H216" s="2" t="n"/>
@@ -6982,7 +7046,7 @@
         <v>36000</v>
       </c>
       <c r="G217" s="8">
-        <f>IFERROR(IF(B217&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B217)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A217)*100+MONTH(A217)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A217)*100+MONTH(A217)))),0)),""),"")</f>
+        <f>IFERROR(IF(B217&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B217)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A217)*100+MONTH(A217)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A217)*100+MONTH(A217)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H217" s="2" t="n"/>
@@ -7010,7 +7074,7 @@
         <v>48000</v>
       </c>
       <c r="G218" s="8">
-        <f>IFERROR(IF(B218&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B218)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A218)*100+MONTH(A218)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A218)*100+MONTH(A218)))),0)),""),"")</f>
+        <f>IFERROR(IF(B218&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B218)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A218)*100+MONTH(A218)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A218)*100+MONTH(A218)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H218" s="2" t="n"/>
@@ -7038,7 +7102,7 @@
         <v>48000</v>
       </c>
       <c r="G219" s="8">
-        <f>IFERROR(IF(B219&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B219)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A219)*100+MONTH(A219)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A219)*100+MONTH(A219)))),0)),""),"")</f>
+        <f>IFERROR(IF(B219&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B219)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A219)*100+MONTH(A219)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A219)*100+MONTH(A219)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H219" s="2" t="n"/>
@@ -7066,7 +7130,7 @@
         <v>36000</v>
       </c>
       <c r="G220" s="8">
-        <f>IFERROR(IF(B220&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B220)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A220)*100+MONTH(A220)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A220)*100+MONTH(A220)))),0)),""),"")</f>
+        <f>IFERROR(IF(B220&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B220)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A220)*100+MONTH(A220)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A220)*100+MONTH(A220)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H220" s="2" t="n"/>
@@ -7094,7 +7158,7 @@
         <v>48000</v>
       </c>
       <c r="G221" s="8">
-        <f>IFERROR(IF(B221&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B221)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A221)*100+MONTH(A221)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A221)*100+MONTH(A221)))),0)),""),"")</f>
+        <f>IFERROR(IF(B221&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B221)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A221)*100+MONTH(A221)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A221)*100+MONTH(A221)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H221" s="2" t="n"/>
@@ -7122,7 +7186,7 @@
         <v>48000</v>
       </c>
       <c r="G222" s="8">
-        <f>IFERROR(IF(B222&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B222)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A222)*100+MONTH(A222)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A222)*100+MONTH(A222)))),0)),""),"")</f>
+        <f>IFERROR(IF(B222&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B222)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A222)*100+MONTH(A222)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A222)*100+MONTH(A222)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H222" s="2" t="n"/>
@@ -7150,7 +7214,7 @@
         <v>36000</v>
       </c>
       <c r="G223" s="8">
-        <f>IFERROR(IF(B223&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B223)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A223)*100+MONTH(A223)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A223)*100+MONTH(A223)))),0)),""),"")</f>
+        <f>IFERROR(IF(B223&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B223)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A223)*100+MONTH(A223)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A223)*100+MONTH(A223)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H223" s="2" t="n"/>
@@ -7178,7 +7242,7 @@
         <v>48000</v>
       </c>
       <c r="G224" s="8">
-        <f>IFERROR(IF(B224&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B224)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A224)*100+MONTH(A224)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A224)*100+MONTH(A224)))),0)),""),"")</f>
+        <f>IFERROR(IF(B224&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B224)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A224)*100+MONTH(A224)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A224)*100+MONTH(A224)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H224" s="2" t="n"/>
@@ -7206,7 +7270,7 @@
         <v>48000</v>
       </c>
       <c r="G225" s="8">
-        <f>IFERROR(IF(B225&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B225)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A225)*100+MONTH(A225)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A225)*100+MONTH(A225)))),0)),""),"")</f>
+        <f>IFERROR(IF(B225&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B225)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A225)*100+MONTH(A225)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A225)*100+MONTH(A225)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H225" s="2" t="n"/>
@@ -7234,7 +7298,7 @@
         <v>36000</v>
       </c>
       <c r="G226" s="8">
-        <f>IFERROR(IF(B226&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B226)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A226)*100+MONTH(A226)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A226)*100+MONTH(A226)))),0)),""),"")</f>
+        <f>IFERROR(IF(B226&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B226)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A226)*100+MONTH(A226)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A226)*100+MONTH(A226)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H226" s="2" t="n"/>
@@ -7262,7 +7326,7 @@
         <v>48000</v>
       </c>
       <c r="G227" s="8">
-        <f>IFERROR(IF(B227&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B227)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A227)*100+MONTH(A227)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A227)*100+MONTH(A227)))),0)),""),"")</f>
+        <f>IFERROR(IF(B227&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B227)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A227)*100+MONTH(A227)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A227)*100+MONTH(A227)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H227" s="2" t="n"/>
@@ -7290,7 +7354,7 @@
         <v>36000</v>
       </c>
       <c r="G228" s="8">
-        <f>IFERROR(IF(B228&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B228)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A228)*100+MONTH(A228)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A228)*100+MONTH(A228)))),0)),""),"")</f>
+        <f>IFERROR(IF(B228&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B228)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A228)*100+MONTH(A228)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A228)*100+MONTH(A228)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H228" s="2" t="n"/>
@@ -7318,7 +7382,7 @@
         <v>48000</v>
       </c>
       <c r="G229" s="8">
-        <f>IFERROR(IF(B229&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B229)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A229)*100+MONTH(A229)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A229)*100+MONTH(A229)))),0)),""),"")</f>
+        <f>IFERROR(IF(B229&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B229)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A229)*100+MONTH(A229)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A229)*100+MONTH(A229)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H229" s="2" t="n"/>
@@ -7346,7 +7410,7 @@
         <v>48000</v>
       </c>
       <c r="G230" s="8">
-        <f>IFERROR(IF(B230&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B230)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A230)*100+MONTH(A230)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A230)*100+MONTH(A230)))),0)),""),"")</f>
+        <f>IFERROR(IF(B230&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B230)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A230)*100+MONTH(A230)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A230)*100+MONTH(A230)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H230" s="2" t="n"/>
@@ -7374,7 +7438,7 @@
         <v>36000</v>
       </c>
       <c r="G231" s="8">
-        <f>IFERROR(IF(B231&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B231)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A231)*100+MONTH(A231)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A231)*100+MONTH(A231)))),0)),""),"")</f>
+        <f>IFERROR(IF(B231&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B231)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A231)*100+MONTH(A231)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A231)*100+MONTH(A231)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H231" s="2" t="n"/>
@@ -7402,7 +7466,7 @@
         <v>48000</v>
       </c>
       <c r="G232" s="8">
-        <f>IFERROR(IF(B232&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B232)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A232)*100+MONTH(A232)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A232)*100+MONTH(A232)))),0)),""),"")</f>
+        <f>IFERROR(IF(B232&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B232)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A232)*100+MONTH(A232)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A232)*100+MONTH(A232)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H232" s="2" t="n"/>
@@ -7430,7 +7494,7 @@
         <v>48000</v>
       </c>
       <c r="G233" s="8">
-        <f>IFERROR(IF(B233&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B233)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A233)*100+MONTH(A233)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A233)*100+MONTH(A233)))),0)),""),"")</f>
+        <f>IFERROR(IF(B233&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B233)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A233)*100+MONTH(A233)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A233)*100+MONTH(A233)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H233" s="2" t="n"/>
@@ -7458,7 +7522,7 @@
         <v>36000</v>
       </c>
       <c r="G234" s="8">
-        <f>IFERROR(IF(B234&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B234)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A234)*100+MONTH(A234)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A234)*100+MONTH(A234)))),0)),""),"")</f>
+        <f>IFERROR(IF(B234&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B234)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A234)*100+MONTH(A234)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A234)*100+MONTH(A234)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H234" s="2" t="n"/>
@@ -7486,7 +7550,7 @@
         <v>48000</v>
       </c>
       <c r="G235" s="8">
-        <f>IFERROR(IF(B235&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B235)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A235)*100+MONTH(A235)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A235)*100+MONTH(A235)))),0)),""),"")</f>
+        <f>IFERROR(IF(B235&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B235)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A235)*100+MONTH(A235)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A235)*100+MONTH(A235)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H235" s="2" t="n"/>
@@ -7514,7 +7578,7 @@
         <v>36000</v>
       </c>
       <c r="G236" s="8">
-        <f>IFERROR(IF(B236&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B236)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A236)*100+MONTH(A236)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A236)*100+MONTH(A236)))),0)),""),"")</f>
+        <f>IFERROR(IF(B236&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B236)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A236)*100+MONTH(A236)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A236)*100+MONTH(A236)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H236" s="2" t="n"/>
@@ -7542,7 +7606,7 @@
         <v>48000</v>
       </c>
       <c r="G237" s="8">
-        <f>IFERROR(IF(B237&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B237)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A237)*100+MONTH(A237)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A237)*100+MONTH(A237)))),0)),""),"")</f>
+        <f>IFERROR(IF(B237&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B237)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A237)*100+MONTH(A237)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A237)*100+MONTH(A237)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H237" s="2" t="n"/>
@@ -7570,7 +7634,7 @@
         <v>48000</v>
       </c>
       <c r="G238" s="8">
-        <f>IFERROR(IF(B238&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B238)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A238)*100+MONTH(A238)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A238)*100+MONTH(A238)))),0)),""),"")</f>
+        <f>IFERROR(IF(B238&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B238)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A238)*100+MONTH(A238)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A238)*100+MONTH(A238)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H238" s="2" t="n"/>
@@ -7585,11 +7649,11 @@
         <v/>
       </c>
       <c r="F239" s="9">
-        <f>IFERROR(IF(AND(B239&lt;&gt;"",G239="시급"),E239*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B239)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A239)*100+MONTH(A239)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A239)*100+MONTH(A239)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B239&lt;&gt;"",G239="시급"),E239*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B239)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A239)*100+MONTH(A239)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A239)*100+MONTH(A239)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G239" s="8">
-        <f>IFERROR(IF(B239&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B239)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A239)*100+MONTH(A239)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A239)*100+MONTH(A239)))),0)),""),"")</f>
+        <f>IFERROR(IF(B239&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B239)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A239)*100+MONTH(A239)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A239)*100+MONTH(A239)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H239" s="2" t="n"/>
@@ -7604,11 +7668,11 @@
         <v/>
       </c>
       <c r="F240" s="9">
-        <f>IFERROR(IF(AND(B240&lt;&gt;"",G240="시급"),E240*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B240)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A240)*100+MONTH(A240)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A240)*100+MONTH(A240)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B240&lt;&gt;"",G240="시급"),E240*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B240)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A240)*100+MONTH(A240)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A240)*100+MONTH(A240)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G240" s="8">
-        <f>IFERROR(IF(B240&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B240)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A240)*100+MONTH(A240)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A240)*100+MONTH(A240)))),0)),""),"")</f>
+        <f>IFERROR(IF(B240&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B240)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A240)*100+MONTH(A240)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A240)*100+MONTH(A240)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H240" s="2" t="n"/>
@@ -7623,11 +7687,11 @@
         <v/>
       </c>
       <c r="F241" s="9">
-        <f>IFERROR(IF(AND(B241&lt;&gt;"",G241="시급"),E241*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B241)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A241)*100+MONTH(A241)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A241)*100+MONTH(A241)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B241&lt;&gt;"",G241="시급"),E241*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B241)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A241)*100+MONTH(A241)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A241)*100+MONTH(A241)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G241" s="8">
-        <f>IFERROR(IF(B241&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B241)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A241)*100+MONTH(A241)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A241)*100+MONTH(A241)))),0)),""),"")</f>
+        <f>IFERROR(IF(B241&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B241)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A241)*100+MONTH(A241)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A241)*100+MONTH(A241)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H241" s="2" t="n"/>
@@ -7642,11 +7706,11 @@
         <v/>
       </c>
       <c r="F242" s="9">
-        <f>IFERROR(IF(AND(B242&lt;&gt;"",G242="시급"),E242*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B242)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A242)*100+MONTH(A242)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A242)*100+MONTH(A242)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B242&lt;&gt;"",G242="시급"),E242*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B242)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A242)*100+MONTH(A242)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A242)*100+MONTH(A242)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G242" s="8">
-        <f>IFERROR(IF(B242&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B242)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A242)*100+MONTH(A242)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A242)*100+MONTH(A242)))),0)),""),"")</f>
+        <f>IFERROR(IF(B242&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B242)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A242)*100+MONTH(A242)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A242)*100+MONTH(A242)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H242" s="2" t="n"/>
@@ -7661,11 +7725,11 @@
         <v/>
       </c>
       <c r="F243" s="9">
-        <f>IFERROR(IF(AND(B243&lt;&gt;"",G243="시급"),E243*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B243)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A243)*100+MONTH(A243)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A243)*100+MONTH(A243)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B243&lt;&gt;"",G243="시급"),E243*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B243)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A243)*100+MONTH(A243)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A243)*100+MONTH(A243)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G243" s="8">
-        <f>IFERROR(IF(B243&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B243)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A243)*100+MONTH(A243)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A243)*100+MONTH(A243)))),0)),""),"")</f>
+        <f>IFERROR(IF(B243&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B243)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A243)*100+MONTH(A243)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A243)*100+MONTH(A243)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H243" s="2" t="n"/>
@@ -7680,11 +7744,11 @@
         <v/>
       </c>
       <c r="F244" s="9">
-        <f>IFERROR(IF(AND(B244&lt;&gt;"",G244="시급"),E244*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B244)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A244)*100+MONTH(A244)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A244)*100+MONTH(A244)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B244&lt;&gt;"",G244="시급"),E244*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B244)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A244)*100+MONTH(A244)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A244)*100+MONTH(A244)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G244" s="8">
-        <f>IFERROR(IF(B244&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B244)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A244)*100+MONTH(A244)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A244)*100+MONTH(A244)))),0)),""),"")</f>
+        <f>IFERROR(IF(B244&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B244)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A244)*100+MONTH(A244)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A244)*100+MONTH(A244)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H244" s="2" t="n"/>
@@ -7699,11 +7763,11 @@
         <v/>
       </c>
       <c r="F245" s="9">
-        <f>IFERROR(IF(AND(B245&lt;&gt;"",G245="시급"),E245*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B245)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A245)*100+MONTH(A245)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A245)*100+MONTH(A245)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B245&lt;&gt;"",G245="시급"),E245*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B245)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A245)*100+MONTH(A245)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A245)*100+MONTH(A245)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G245" s="8">
-        <f>IFERROR(IF(B245&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B245)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A245)*100+MONTH(A245)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A245)*100+MONTH(A245)))),0)),""),"")</f>
+        <f>IFERROR(IF(B245&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B245)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A245)*100+MONTH(A245)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A245)*100+MONTH(A245)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H245" s="2" t="n"/>
@@ -7718,11 +7782,11 @@
         <v/>
       </c>
       <c r="F246" s="9">
-        <f>IFERROR(IF(AND(B246&lt;&gt;"",G246="시급"),E246*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B246)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A246)*100+MONTH(A246)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A246)*100+MONTH(A246)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B246&lt;&gt;"",G246="시급"),E246*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B246)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A246)*100+MONTH(A246)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A246)*100+MONTH(A246)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G246" s="8">
-        <f>IFERROR(IF(B246&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B246)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A246)*100+MONTH(A246)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A246)*100+MONTH(A246)))),0)),""),"")</f>
+        <f>IFERROR(IF(B246&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B246)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A246)*100+MONTH(A246)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A246)*100+MONTH(A246)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H246" s="2" t="n"/>
@@ -7737,11 +7801,11 @@
         <v/>
       </c>
       <c r="F247" s="9">
-        <f>IFERROR(IF(AND(B247&lt;&gt;"",G247="시급"),E247*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B247)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A247)*100+MONTH(A247)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A247)*100+MONTH(A247)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B247&lt;&gt;"",G247="시급"),E247*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B247)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A247)*100+MONTH(A247)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A247)*100+MONTH(A247)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G247" s="8">
-        <f>IFERROR(IF(B247&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B247)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A247)*100+MONTH(A247)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A247)*100+MONTH(A247)))),0)),""),"")</f>
+        <f>IFERROR(IF(B247&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B247)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A247)*100+MONTH(A247)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A247)*100+MONTH(A247)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H247" s="2" t="n"/>
@@ -7756,11 +7820,11 @@
         <v/>
       </c>
       <c r="F248" s="9">
-        <f>IFERROR(IF(AND(B248&lt;&gt;"",G248="시급"),E248*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B248)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A248)*100+MONTH(A248)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A248)*100+MONTH(A248)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B248&lt;&gt;"",G248="시급"),E248*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B248)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A248)*100+MONTH(A248)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A248)*100+MONTH(A248)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G248" s="8">
-        <f>IFERROR(IF(B248&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B248)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A248)*100+MONTH(A248)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A248)*100+MONTH(A248)))),0)),""),"")</f>
+        <f>IFERROR(IF(B248&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B248)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A248)*100+MONTH(A248)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A248)*100+MONTH(A248)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H248" s="2" t="n"/>
@@ -7775,11 +7839,11 @@
         <v/>
       </c>
       <c r="F249" s="9">
-        <f>IFERROR(IF(AND(B249&lt;&gt;"",G249="시급"),E249*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B249)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A249)*100+MONTH(A249)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A249)*100+MONTH(A249)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B249&lt;&gt;"",G249="시급"),E249*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B249)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A249)*100+MONTH(A249)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A249)*100+MONTH(A249)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G249" s="8">
-        <f>IFERROR(IF(B249&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B249)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A249)*100+MONTH(A249)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A249)*100+MONTH(A249)))),0)),""),"")</f>
+        <f>IFERROR(IF(B249&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B249)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A249)*100+MONTH(A249)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A249)*100+MONTH(A249)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H249" s="2" t="n"/>
@@ -7794,11 +7858,11 @@
         <v/>
       </c>
       <c r="F250" s="9">
-        <f>IFERROR(IF(AND(B250&lt;&gt;"",G250="시급"),E250*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B250)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A250)*100+MONTH(A250)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A250)*100+MONTH(A250)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B250&lt;&gt;"",G250="시급"),E250*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B250)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A250)*100+MONTH(A250)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A250)*100+MONTH(A250)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G250" s="8">
-        <f>IFERROR(IF(B250&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B250)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A250)*100+MONTH(A250)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A250)*100+MONTH(A250)))),0)),""),"")</f>
+        <f>IFERROR(IF(B250&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B250)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A250)*100+MONTH(A250)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A250)*100+MONTH(A250)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H250" s="2" t="n"/>
@@ -7813,11 +7877,11 @@
         <v/>
       </c>
       <c r="F251" s="9">
-        <f>IFERROR(IF(AND(B251&lt;&gt;"",G251="시급"),E251*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B251)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A251)*100+MONTH(A251)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A251)*100+MONTH(A251)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B251&lt;&gt;"",G251="시급"),E251*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B251)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A251)*100+MONTH(A251)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A251)*100+MONTH(A251)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G251" s="8">
-        <f>IFERROR(IF(B251&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B251)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A251)*100+MONTH(A251)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A251)*100+MONTH(A251)))),0)),""),"")</f>
+        <f>IFERROR(IF(B251&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B251)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A251)*100+MONTH(A251)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A251)*100+MONTH(A251)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H251" s="2" t="n"/>
@@ -7832,11 +7896,11 @@
         <v/>
       </c>
       <c r="F252" s="9">
-        <f>IFERROR(IF(AND(B252&lt;&gt;"",G252="시급"),E252*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B252)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A252)*100+MONTH(A252)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A252)*100+MONTH(A252)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B252&lt;&gt;"",G252="시급"),E252*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B252)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A252)*100+MONTH(A252)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A252)*100+MONTH(A252)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G252" s="8">
-        <f>IFERROR(IF(B252&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B252)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A252)*100+MONTH(A252)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A252)*100+MONTH(A252)))),0)),""),"")</f>
+        <f>IFERROR(IF(B252&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B252)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A252)*100+MONTH(A252)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A252)*100+MONTH(A252)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H252" s="2" t="n"/>
@@ -7851,11 +7915,11 @@
         <v/>
       </c>
       <c r="F253" s="9">
-        <f>IFERROR(IF(AND(B253&lt;&gt;"",G253="시급"),E253*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B253)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A253)*100+MONTH(A253)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A253)*100+MONTH(A253)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B253&lt;&gt;"",G253="시급"),E253*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B253)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A253)*100+MONTH(A253)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A253)*100+MONTH(A253)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G253" s="8">
-        <f>IFERROR(IF(B253&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B253)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A253)*100+MONTH(A253)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A253)*100+MONTH(A253)))),0)),""),"")</f>
+        <f>IFERROR(IF(B253&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B253)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A253)*100+MONTH(A253)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A253)*100+MONTH(A253)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H253" s="2" t="n"/>
@@ -7870,11 +7934,11 @@
         <v/>
       </c>
       <c r="F254" s="9">
-        <f>IFERROR(IF(AND(B254&lt;&gt;"",G254="시급"),E254*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B254)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A254)*100+MONTH(A254)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A254)*100+MONTH(A254)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B254&lt;&gt;"",G254="시급"),E254*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B254)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A254)*100+MONTH(A254)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A254)*100+MONTH(A254)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G254" s="8">
-        <f>IFERROR(IF(B254&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B254)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A254)*100+MONTH(A254)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A254)*100+MONTH(A254)))),0)),""),"")</f>
+        <f>IFERROR(IF(B254&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B254)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A254)*100+MONTH(A254)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A254)*100+MONTH(A254)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H254" s="2" t="n"/>
@@ -7889,11 +7953,11 @@
         <v/>
       </c>
       <c r="F255" s="9">
-        <f>IFERROR(IF(AND(B255&lt;&gt;"",G255="시급"),E255*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B255)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A255)*100+MONTH(A255)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A255)*100+MONTH(A255)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B255&lt;&gt;"",G255="시급"),E255*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B255)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A255)*100+MONTH(A255)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A255)*100+MONTH(A255)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G255" s="8">
-        <f>IFERROR(IF(B255&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B255)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A255)*100+MONTH(A255)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A255)*100+MONTH(A255)))),0)),""),"")</f>
+        <f>IFERROR(IF(B255&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B255)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A255)*100+MONTH(A255)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A255)*100+MONTH(A255)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H255" s="2" t="n"/>
@@ -7908,11 +7972,11 @@
         <v/>
       </c>
       <c r="F256" s="9">
-        <f>IFERROR(IF(AND(B256&lt;&gt;"",G256="시급"),E256*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B256)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A256)*100+MONTH(A256)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A256)*100+MONTH(A256)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B256&lt;&gt;"",G256="시급"),E256*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B256)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A256)*100+MONTH(A256)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A256)*100+MONTH(A256)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G256" s="8">
-        <f>IFERROR(IF(B256&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B256)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A256)*100+MONTH(A256)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A256)*100+MONTH(A256)))),0)),""),"")</f>
+        <f>IFERROR(IF(B256&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B256)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A256)*100+MONTH(A256)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A256)*100+MONTH(A256)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H256" s="2" t="n"/>
@@ -7927,11 +7991,11 @@
         <v/>
       </c>
       <c r="F257" s="9">
-        <f>IFERROR(IF(AND(B257&lt;&gt;"",G257="시급"),E257*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B257)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A257)*100+MONTH(A257)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A257)*100+MONTH(A257)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B257&lt;&gt;"",G257="시급"),E257*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B257)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A257)*100+MONTH(A257)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A257)*100+MONTH(A257)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G257" s="8">
-        <f>IFERROR(IF(B257&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B257)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A257)*100+MONTH(A257)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A257)*100+MONTH(A257)))),0)),""),"")</f>
+        <f>IFERROR(IF(B257&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B257)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A257)*100+MONTH(A257)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A257)*100+MONTH(A257)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H257" s="2" t="n"/>
@@ -7946,11 +8010,11 @@
         <v/>
       </c>
       <c r="F258" s="9">
-        <f>IFERROR(IF(AND(B258&lt;&gt;"",G258="시급"),E258*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B258)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A258)*100+MONTH(A258)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A258)*100+MONTH(A258)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B258&lt;&gt;"",G258="시급"),E258*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B258)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A258)*100+MONTH(A258)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A258)*100+MONTH(A258)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G258" s="8">
-        <f>IFERROR(IF(B258&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B258)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A258)*100+MONTH(A258)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A258)*100+MONTH(A258)))),0)),""),"")</f>
+        <f>IFERROR(IF(B258&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B258)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A258)*100+MONTH(A258)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A258)*100+MONTH(A258)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H258" s="2" t="n"/>
@@ -7965,11 +8029,11 @@
         <v/>
       </c>
       <c r="F259" s="9">
-        <f>IFERROR(IF(AND(B259&lt;&gt;"",G259="시급"),E259*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B259)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A259)*100+MONTH(A259)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A259)*100+MONTH(A259)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B259&lt;&gt;"",G259="시급"),E259*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B259)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A259)*100+MONTH(A259)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A259)*100+MONTH(A259)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G259" s="8">
-        <f>IFERROR(IF(B259&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B259)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A259)*100+MONTH(A259)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A259)*100+MONTH(A259)))),0)),""),"")</f>
+        <f>IFERROR(IF(B259&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B259)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A259)*100+MONTH(A259)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A259)*100+MONTH(A259)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H259" s="2" t="n"/>
@@ -7984,11 +8048,11 @@
         <v/>
       </c>
       <c r="F260" s="9">
-        <f>IFERROR(IF(AND(B260&lt;&gt;"",G260="시급"),E260*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B260)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A260)*100+MONTH(A260)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A260)*100+MONTH(A260)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B260&lt;&gt;"",G260="시급"),E260*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B260)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A260)*100+MONTH(A260)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A260)*100+MONTH(A260)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G260" s="8">
-        <f>IFERROR(IF(B260&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B260)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A260)*100+MONTH(A260)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A260)*100+MONTH(A260)))),0)),""),"")</f>
+        <f>IFERROR(IF(B260&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B260)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A260)*100+MONTH(A260)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A260)*100+MONTH(A260)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H260" s="2" t="n"/>
@@ -8003,11 +8067,11 @@
         <v/>
       </c>
       <c r="F261" s="9">
-        <f>IFERROR(IF(AND(B261&lt;&gt;"",G261="시급"),E261*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B261)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A261)*100+MONTH(A261)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A261)*100+MONTH(A261)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B261&lt;&gt;"",G261="시급"),E261*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B261)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A261)*100+MONTH(A261)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A261)*100+MONTH(A261)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G261" s="8">
-        <f>IFERROR(IF(B261&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B261)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A261)*100+MONTH(A261)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A261)*100+MONTH(A261)))),0)),""),"")</f>
+        <f>IFERROR(IF(B261&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B261)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A261)*100+MONTH(A261)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A261)*100+MONTH(A261)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H261" s="2" t="n"/>
@@ -8022,11 +8086,11 @@
         <v/>
       </c>
       <c r="F262" s="9">
-        <f>IFERROR(IF(AND(B262&lt;&gt;"",G262="시급"),E262*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B262)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A262)*100+MONTH(A262)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A262)*100+MONTH(A262)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B262&lt;&gt;"",G262="시급"),E262*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B262)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A262)*100+MONTH(A262)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A262)*100+MONTH(A262)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G262" s="8">
-        <f>IFERROR(IF(B262&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B262)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A262)*100+MONTH(A262)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A262)*100+MONTH(A262)))),0)),""),"")</f>
+        <f>IFERROR(IF(B262&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B262)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A262)*100+MONTH(A262)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A262)*100+MONTH(A262)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H262" s="2" t="n"/>
@@ -8041,11 +8105,11 @@
         <v/>
       </c>
       <c r="F263" s="9">
-        <f>IFERROR(IF(AND(B263&lt;&gt;"",G263="시급"),E263*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B263)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A263)*100+MONTH(A263)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A263)*100+MONTH(A263)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B263&lt;&gt;"",G263="시급"),E263*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B263)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A263)*100+MONTH(A263)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A263)*100+MONTH(A263)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G263" s="8">
-        <f>IFERROR(IF(B263&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B263)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A263)*100+MONTH(A263)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A263)*100+MONTH(A263)))),0)),""),"")</f>
+        <f>IFERROR(IF(B263&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B263)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A263)*100+MONTH(A263)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A263)*100+MONTH(A263)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H263" s="2" t="n"/>
@@ -8060,11 +8124,11 @@
         <v/>
       </c>
       <c r="F264" s="9">
-        <f>IFERROR(IF(AND(B264&lt;&gt;"",G264="시급"),E264*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B264)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A264)*100+MONTH(A264)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A264)*100+MONTH(A264)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B264&lt;&gt;"",G264="시급"),E264*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B264)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A264)*100+MONTH(A264)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A264)*100+MONTH(A264)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G264" s="8">
-        <f>IFERROR(IF(B264&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B264)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A264)*100+MONTH(A264)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A264)*100+MONTH(A264)))),0)),""),"")</f>
+        <f>IFERROR(IF(B264&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B264)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A264)*100+MONTH(A264)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A264)*100+MONTH(A264)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H264" s="2" t="n"/>
@@ -8079,11 +8143,11 @@
         <v/>
       </c>
       <c r="F265" s="9">
-        <f>IFERROR(IF(AND(B265&lt;&gt;"",G265="시급"),E265*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B265)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A265)*100+MONTH(A265)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A265)*100+MONTH(A265)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B265&lt;&gt;"",G265="시급"),E265*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B265)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A265)*100+MONTH(A265)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A265)*100+MONTH(A265)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G265" s="8">
-        <f>IFERROR(IF(B265&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B265)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A265)*100+MONTH(A265)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A265)*100+MONTH(A265)))),0)),""),"")</f>
+        <f>IFERROR(IF(B265&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B265)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A265)*100+MONTH(A265)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A265)*100+MONTH(A265)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H265" s="2" t="n"/>
@@ -8098,11 +8162,11 @@
         <v/>
       </c>
       <c r="F266" s="9">
-        <f>IFERROR(IF(AND(B266&lt;&gt;"",G266="시급"),E266*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B266)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A266)*100+MONTH(A266)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A266)*100+MONTH(A266)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B266&lt;&gt;"",G266="시급"),E266*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B266)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A266)*100+MONTH(A266)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A266)*100+MONTH(A266)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G266" s="8">
-        <f>IFERROR(IF(B266&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B266)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A266)*100+MONTH(A266)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A266)*100+MONTH(A266)))),0)),""),"")</f>
+        <f>IFERROR(IF(B266&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B266)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A266)*100+MONTH(A266)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A266)*100+MONTH(A266)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H266" s="2" t="n"/>
@@ -8117,11 +8181,11 @@
         <v/>
       </c>
       <c r="F267" s="9">
-        <f>IFERROR(IF(AND(B267&lt;&gt;"",G267="시급"),E267*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B267)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A267)*100+MONTH(A267)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A267)*100+MONTH(A267)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B267&lt;&gt;"",G267="시급"),E267*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B267)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A267)*100+MONTH(A267)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A267)*100+MONTH(A267)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G267" s="8">
-        <f>IFERROR(IF(B267&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B267)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A267)*100+MONTH(A267)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A267)*100+MONTH(A267)))),0)),""),"")</f>
+        <f>IFERROR(IF(B267&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B267)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A267)*100+MONTH(A267)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A267)*100+MONTH(A267)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H267" s="2" t="n"/>
@@ -8136,11 +8200,11 @@
         <v/>
       </c>
       <c r="F268" s="9">
-        <f>IFERROR(IF(AND(B268&lt;&gt;"",G268="시급"),E268*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B268)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A268)*100+MONTH(A268)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A268)*100+MONTH(A268)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B268&lt;&gt;"",G268="시급"),E268*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B268)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A268)*100+MONTH(A268)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A268)*100+MONTH(A268)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G268" s="8">
-        <f>IFERROR(IF(B268&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B268)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A268)*100+MONTH(A268)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A268)*100+MONTH(A268)))),0)),""),"")</f>
+        <f>IFERROR(IF(B268&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B268)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A268)*100+MONTH(A268)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A268)*100+MONTH(A268)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H268" s="2" t="n"/>
@@ -8155,11 +8219,11 @@
         <v/>
       </c>
       <c r="F269" s="9">
-        <f>IFERROR(IF(AND(B269&lt;&gt;"",G269="시급"),E269*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B269)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A269)*100+MONTH(A269)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A269)*100+MONTH(A269)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B269&lt;&gt;"",G269="시급"),E269*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B269)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A269)*100+MONTH(A269)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A269)*100+MONTH(A269)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G269" s="8">
-        <f>IFERROR(IF(B269&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B269)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A269)*100+MONTH(A269)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A269)*100+MONTH(A269)))),0)),""),"")</f>
+        <f>IFERROR(IF(B269&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B269)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A269)*100+MONTH(A269)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A269)*100+MONTH(A269)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H269" s="2" t="n"/>
@@ -8174,11 +8238,11 @@
         <v/>
       </c>
       <c r="F270" s="9">
-        <f>IFERROR(IF(AND(B270&lt;&gt;"",G270="시급"),E270*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B270)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A270)*100+MONTH(A270)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A270)*100+MONTH(A270)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B270&lt;&gt;"",G270="시급"),E270*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B270)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A270)*100+MONTH(A270)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A270)*100+MONTH(A270)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G270" s="8">
-        <f>IFERROR(IF(B270&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B270)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A270)*100+MONTH(A270)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A270)*100+MONTH(A270)))),0)),""),"")</f>
+        <f>IFERROR(IF(B270&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B270)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A270)*100+MONTH(A270)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A270)*100+MONTH(A270)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H270" s="2" t="n"/>
@@ -8193,11 +8257,11 @@
         <v/>
       </c>
       <c r="F271" s="9">
-        <f>IFERROR(IF(AND(B271&lt;&gt;"",G271="시급"),E271*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B271)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A271)*100+MONTH(A271)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A271)*100+MONTH(A271)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B271&lt;&gt;"",G271="시급"),E271*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B271)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A271)*100+MONTH(A271)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A271)*100+MONTH(A271)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G271" s="8">
-        <f>IFERROR(IF(B271&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B271)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A271)*100+MONTH(A271)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A271)*100+MONTH(A271)))),0)),""),"")</f>
+        <f>IFERROR(IF(B271&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B271)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A271)*100+MONTH(A271)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A271)*100+MONTH(A271)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H271" s="2" t="n"/>
@@ -8212,11 +8276,11 @@
         <v/>
       </c>
       <c r="F272" s="9">
-        <f>IFERROR(IF(AND(B272&lt;&gt;"",G272="시급"),E272*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B272)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A272)*100+MONTH(A272)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A272)*100+MONTH(A272)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B272&lt;&gt;"",G272="시급"),E272*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B272)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A272)*100+MONTH(A272)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A272)*100+MONTH(A272)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G272" s="8">
-        <f>IFERROR(IF(B272&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B272)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A272)*100+MONTH(A272)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A272)*100+MONTH(A272)))),0)),""),"")</f>
+        <f>IFERROR(IF(B272&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B272)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A272)*100+MONTH(A272)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A272)*100+MONTH(A272)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H272" s="2" t="n"/>
@@ -8231,11 +8295,11 @@
         <v/>
       </c>
       <c r="F273" s="9">
-        <f>IFERROR(IF(AND(B273&lt;&gt;"",G273="시급"),E273*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B273)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A273)*100+MONTH(A273)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A273)*100+MONTH(A273)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B273&lt;&gt;"",G273="시급"),E273*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B273)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A273)*100+MONTH(A273)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A273)*100+MONTH(A273)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G273" s="8">
-        <f>IFERROR(IF(B273&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B273)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A273)*100+MONTH(A273)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A273)*100+MONTH(A273)))),0)),""),"")</f>
+        <f>IFERROR(IF(B273&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B273)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A273)*100+MONTH(A273)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A273)*100+MONTH(A273)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H273" s="2" t="n"/>
@@ -8250,11 +8314,11 @@
         <v/>
       </c>
       <c r="F274" s="9">
-        <f>IFERROR(IF(AND(B274&lt;&gt;"",G274="시급"),E274*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B274)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A274)*100+MONTH(A274)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A274)*100+MONTH(A274)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B274&lt;&gt;"",G274="시급"),E274*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B274)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A274)*100+MONTH(A274)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A274)*100+MONTH(A274)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G274" s="8">
-        <f>IFERROR(IF(B274&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B274)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A274)*100+MONTH(A274)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A274)*100+MONTH(A274)))),0)),""),"")</f>
+        <f>IFERROR(IF(B274&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B274)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A274)*100+MONTH(A274)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A274)*100+MONTH(A274)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H274" s="2" t="n"/>
@@ -8269,11 +8333,11 @@
         <v/>
       </c>
       <c r="F275" s="9">
-        <f>IFERROR(IF(AND(B275&lt;&gt;"",G275="시급"),E275*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B275)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A275)*100+MONTH(A275)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A275)*100+MONTH(A275)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B275&lt;&gt;"",G275="시급"),E275*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B275)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A275)*100+MONTH(A275)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A275)*100+MONTH(A275)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G275" s="8">
-        <f>IFERROR(IF(B275&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B275)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A275)*100+MONTH(A275)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A275)*100+MONTH(A275)))),0)),""),"")</f>
+        <f>IFERROR(IF(B275&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B275)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A275)*100+MONTH(A275)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A275)*100+MONTH(A275)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H275" s="2" t="n"/>
@@ -8288,11 +8352,11 @@
         <v/>
       </c>
       <c r="F276" s="9">
-        <f>IFERROR(IF(AND(B276&lt;&gt;"",G276="시급"),E276*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B276)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A276)*100+MONTH(A276)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A276)*100+MONTH(A276)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B276&lt;&gt;"",G276="시급"),E276*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B276)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A276)*100+MONTH(A276)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A276)*100+MONTH(A276)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G276" s="8">
-        <f>IFERROR(IF(B276&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B276)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A276)*100+MONTH(A276)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A276)*100+MONTH(A276)))),0)),""),"")</f>
+        <f>IFERROR(IF(B276&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B276)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A276)*100+MONTH(A276)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A276)*100+MONTH(A276)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H276" s="2" t="n"/>
@@ -8307,11 +8371,11 @@
         <v/>
       </c>
       <c r="F277" s="9">
-        <f>IFERROR(IF(AND(B277&lt;&gt;"",G277="시급"),E277*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B277)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A277)*100+MONTH(A277)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A277)*100+MONTH(A277)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B277&lt;&gt;"",G277="시급"),E277*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B277)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A277)*100+MONTH(A277)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A277)*100+MONTH(A277)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G277" s="8">
-        <f>IFERROR(IF(B277&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B277)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A277)*100+MONTH(A277)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A277)*100+MONTH(A277)))),0)),""),"")</f>
+        <f>IFERROR(IF(B277&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B277)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A277)*100+MONTH(A277)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A277)*100+MONTH(A277)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H277" s="2" t="n"/>
@@ -8326,11 +8390,11 @@
         <v/>
       </c>
       <c r="F278" s="9">
-        <f>IFERROR(IF(AND(B278&lt;&gt;"",G278="시급"),E278*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B278)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A278)*100+MONTH(A278)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A278)*100+MONTH(A278)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B278&lt;&gt;"",G278="시급"),E278*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B278)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A278)*100+MONTH(A278)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A278)*100+MONTH(A278)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G278" s="8">
-        <f>IFERROR(IF(B278&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B278)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A278)*100+MONTH(A278)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A278)*100+MONTH(A278)))),0)),""),"")</f>
+        <f>IFERROR(IF(B278&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B278)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A278)*100+MONTH(A278)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A278)*100+MONTH(A278)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H278" s="2" t="n"/>
@@ -8345,11 +8409,11 @@
         <v/>
       </c>
       <c r="F279" s="9">
-        <f>IFERROR(IF(AND(B279&lt;&gt;"",G279="시급"),E279*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B279)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A279)*100+MONTH(A279)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A279)*100+MONTH(A279)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B279&lt;&gt;"",G279="시급"),E279*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B279)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A279)*100+MONTH(A279)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A279)*100+MONTH(A279)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G279" s="8">
-        <f>IFERROR(IF(B279&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B279)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A279)*100+MONTH(A279)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A279)*100+MONTH(A279)))),0)),""),"")</f>
+        <f>IFERROR(IF(B279&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B279)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A279)*100+MONTH(A279)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A279)*100+MONTH(A279)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H279" s="2" t="n"/>
@@ -8364,11 +8428,11 @@
         <v/>
       </c>
       <c r="F280" s="9">
-        <f>IFERROR(IF(AND(B280&lt;&gt;"",G280="시급"),E280*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B280)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A280)*100+MONTH(A280)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A280)*100+MONTH(A280)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B280&lt;&gt;"",G280="시급"),E280*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B280)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A280)*100+MONTH(A280)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A280)*100+MONTH(A280)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G280" s="8">
-        <f>IFERROR(IF(B280&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B280)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A280)*100+MONTH(A280)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A280)*100+MONTH(A280)))),0)),""),"")</f>
+        <f>IFERROR(IF(B280&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B280)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A280)*100+MONTH(A280)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A280)*100+MONTH(A280)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H280" s="2" t="n"/>
@@ -8383,11 +8447,11 @@
         <v/>
       </c>
       <c r="F281" s="9">
-        <f>IFERROR(IF(AND(B281&lt;&gt;"",G281="시급"),E281*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B281)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A281)*100+MONTH(A281)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A281)*100+MONTH(A281)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B281&lt;&gt;"",G281="시급"),E281*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B281)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A281)*100+MONTH(A281)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A281)*100+MONTH(A281)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G281" s="8">
-        <f>IFERROR(IF(B281&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B281)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A281)*100+MONTH(A281)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A281)*100+MONTH(A281)))),0)),""),"")</f>
+        <f>IFERROR(IF(B281&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B281)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A281)*100+MONTH(A281)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A281)*100+MONTH(A281)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H281" s="2" t="n"/>
@@ -8402,11 +8466,11 @@
         <v/>
       </c>
       <c r="F282" s="9">
-        <f>IFERROR(IF(AND(B282&lt;&gt;"",G282="시급"),E282*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B282)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A282)*100+MONTH(A282)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A282)*100+MONTH(A282)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B282&lt;&gt;"",G282="시급"),E282*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B282)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A282)*100+MONTH(A282)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A282)*100+MONTH(A282)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G282" s="8">
-        <f>IFERROR(IF(B282&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B282)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A282)*100+MONTH(A282)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A282)*100+MONTH(A282)))),0)),""),"")</f>
+        <f>IFERROR(IF(B282&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B282)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A282)*100+MONTH(A282)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A282)*100+MONTH(A282)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H282" s="2" t="n"/>
@@ -8421,11 +8485,11 @@
         <v/>
       </c>
       <c r="F283" s="9">
-        <f>IFERROR(IF(AND(B283&lt;&gt;"",G283="시급"),E283*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B283)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A283)*100+MONTH(A283)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A283)*100+MONTH(A283)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B283&lt;&gt;"",G283="시급"),E283*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B283)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A283)*100+MONTH(A283)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A283)*100+MONTH(A283)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G283" s="8">
-        <f>IFERROR(IF(B283&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B283)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A283)*100+MONTH(A283)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A283)*100+MONTH(A283)))),0)),""),"")</f>
+        <f>IFERROR(IF(B283&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B283)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A283)*100+MONTH(A283)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A283)*100+MONTH(A283)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H283" s="2" t="n"/>
@@ -8440,11 +8504,11 @@
         <v/>
       </c>
       <c r="F284" s="9">
-        <f>IFERROR(IF(AND(B284&lt;&gt;"",G284="시급"),E284*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B284)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A284)*100+MONTH(A284)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A284)*100+MONTH(A284)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B284&lt;&gt;"",G284="시급"),E284*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B284)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A284)*100+MONTH(A284)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A284)*100+MONTH(A284)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G284" s="8">
-        <f>IFERROR(IF(B284&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B284)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A284)*100+MONTH(A284)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A284)*100+MONTH(A284)))),0)),""),"")</f>
+        <f>IFERROR(IF(B284&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B284)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A284)*100+MONTH(A284)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A284)*100+MONTH(A284)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H284" s="2" t="n"/>
@@ -8459,11 +8523,11 @@
         <v/>
       </c>
       <c r="F285" s="9">
-        <f>IFERROR(IF(AND(B285&lt;&gt;"",G285="시급"),E285*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B285)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A285)*100+MONTH(A285)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A285)*100+MONTH(A285)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B285&lt;&gt;"",G285="시급"),E285*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B285)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A285)*100+MONTH(A285)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A285)*100+MONTH(A285)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G285" s="8">
-        <f>IFERROR(IF(B285&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B285)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A285)*100+MONTH(A285)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A285)*100+MONTH(A285)))),0)),""),"")</f>
+        <f>IFERROR(IF(B285&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B285)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A285)*100+MONTH(A285)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A285)*100+MONTH(A285)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H285" s="2" t="n"/>
@@ -8478,11 +8542,11 @@
         <v/>
       </c>
       <c r="F286" s="9">
-        <f>IFERROR(IF(AND(B286&lt;&gt;"",G286="시급"),E286*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B286)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A286)*100+MONTH(A286)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A286)*100+MONTH(A286)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B286&lt;&gt;"",G286="시급"),E286*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B286)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A286)*100+MONTH(A286)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A286)*100+MONTH(A286)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G286" s="8">
-        <f>IFERROR(IF(B286&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B286)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A286)*100+MONTH(A286)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A286)*100+MONTH(A286)))),0)),""),"")</f>
+        <f>IFERROR(IF(B286&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B286)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A286)*100+MONTH(A286)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A286)*100+MONTH(A286)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H286" s="2" t="n"/>
@@ -8497,11 +8561,11 @@
         <v/>
       </c>
       <c r="F287" s="9">
-        <f>IFERROR(IF(AND(B287&lt;&gt;"",G287="시급"),E287*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B287)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A287)*100+MONTH(A287)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A287)*100+MONTH(A287)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B287&lt;&gt;"",G287="시급"),E287*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B287)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A287)*100+MONTH(A287)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A287)*100+MONTH(A287)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G287" s="8">
-        <f>IFERROR(IF(B287&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B287)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A287)*100+MONTH(A287)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A287)*100+MONTH(A287)))),0)),""),"")</f>
+        <f>IFERROR(IF(B287&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B287)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A287)*100+MONTH(A287)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A287)*100+MONTH(A287)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H287" s="2" t="n"/>
@@ -8516,11 +8580,11 @@
         <v/>
       </c>
       <c r="F288" s="9">
-        <f>IFERROR(IF(AND(B288&lt;&gt;"",G288="시급"),E288*24*INDEX('직원 마스터'!C$2:C$29,MATCH(1,('직원 마스터'!A$2:A$29=B288)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A288)*100+MONTH(A288)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A288)*100+MONTH(A288)))),0)),0),0)</f>
+        <f>IFERROR(IF(AND(B288&lt;&gt;"",G288="시급"),E288*24*INDEX('직원 마스터'!C$2:C$31,MATCH(1,('직원 마스터'!A$2:A$31=B288)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A288)*100+MONTH(A288)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A288)*100+MONTH(A288)))),0)),0),0)</f>
         <v/>
       </c>
       <c r="G288" s="8">
-        <f>IFERROR(IF(B288&lt;&gt;"",INDEX('직원 마스터'!B$2:B$29,MATCH(1,('직원 마스터'!A$2:A$29=B288)*('직원 마스터'!F$2:F$29&lt;=(YEAR(A288)*100+MONTH(A288)))*(('직원 마스터'!G$2:G$29="")+('직원 마스터'!G$2:G$29&gt;=(YEAR(A288)*100+MONTH(A288)))),0)),""),"")</f>
+        <f>IFERROR(IF(B288&lt;&gt;"",INDEX('직원 마스터'!B$2:B$31,MATCH(1,('직원 마스터'!A$2:A$31=B288)*('직원 마스터'!F$2:F$31&lt;=(YEAR(A288)*100+MONTH(A288)))*(('직원 마스터'!G$2:G$31="")+('직원 마스터'!G$2:G$31&gt;=(YEAR(A288)*100+MONTH(A288)))),0)),""),"")</f>
         <v/>
       </c>
       <c r="H288" s="2" t="n"/>
@@ -8529,7 +8593,7 @@
   <autoFilter ref="A1:H288"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B288" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"고경민,고경민,고경민,장예원,유은비,전민아,김채현,이진화"</formula1>
+      <formula1>"고경민,고경민,고경민,장예원,유은비,전민아,전민아,전민아,김채현,이진화"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9106,7 +9170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9456,41 +9520,109 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" s="2">
+        <f>IF(AND('직원 마스터'!F10&lt;&gt;"",'직원 마스터'!F10&lt;=$B$1,OR('직원 마스터'!G10="",'직원 마스터'!G10&gt;=$B$1)),'직원 마스터'!A10,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2">
+        <f>IF(AND('직원 마스터'!F10&lt;&gt;"",'직원 마스터'!F10&lt;=$B$1,OR('직원 마스터'!G10="",'직원 마스터'!G10&gt;=$B$1)),'직원 마스터'!B10,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>IF(AND('직원 마스터'!F10&lt;&gt;"",'직원 마스터'!F10&lt;=$B$1,OR('직원 마스터'!G10="",'직원 마스터'!G10&gt;=$B$1)),SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A10)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!E$2:E$500))*24,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
+        <f>IF(B12="","",IF(C12="월급",'직원 마스터'!C10,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A10)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>IF(E12="","",ROUND(E12*0.033,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>IF(E12="","",E12-F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="2">
+        <f>IF(B12="","",'직원 마스터'!D10)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B12)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+        <v/>
+      </c>
+    </row>
     <row r="13">
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="2">
+        <f>IF(AND('직원 마스터'!F11&lt;&gt;"",'직원 마스터'!F11&lt;=$B$1,OR('직원 마스터'!G11="",'직원 마스터'!G11&gt;=$B$1)),'직원 마스터'!A11,"")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2">
+        <f>IF(AND('직원 마스터'!F11&lt;&gt;"",'직원 마스터'!F11&lt;=$B$1,OR('직원 마스터'!G11="",'직원 마스터'!G11&gt;=$B$1)),'직원 마스터'!B11,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>IF(AND('직원 마스터'!F11&lt;&gt;"",'직원 마스터'!F11&lt;=$B$1,OR('직원 마스터'!G11="",'직원 마스터'!G11&gt;=$B$1)),SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A11)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!E$2:E$500))*24,"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
+        <f>IF(B13="","",IF(C13="월급",'직원 마스터'!C11,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A11)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>IF(E13="","",ROUND(E13*0.033,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>IF(E13="","",E13-F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="2">
+        <f>IF(B13="","",'직원 마스터'!D11)</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B13)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E13" s="19">
-        <f>SUM(E4:E11)</f>
-        <v/>
-      </c>
-      <c r="F13" s="19">
-        <f>SUM(F4:F11)</f>
-        <v/>
-      </c>
-      <c r="G13" s="19">
-        <f>SUM(G4:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="20" t="inlineStr">
+      <c r="E15" s="19">
+        <f>SUM(E4:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="19">
+        <f>SUM(F4:F13)</f>
+        <v/>
+      </c>
+      <c r="G15" s="19">
+        <f>SUM(G4:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>당월 총 인건비</t>
         </is>
       </c>
-      <c r="E14" s="21">
-        <f>E13</f>
+      <c r="E16" s="21">
+        <f>E15</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:I11">
+  <conditionalFormatting sqref="I4:I13">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"O"</formula>
     </cfRule>
@@ -9502,7 +9634,7 @@
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"202501,202502,202503,202504,202505,202506,202507,202508,202509,202510,202511,202512"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
     </dataValidation>
   </dataValidations>

--- a/BUNT_finance/분트_인건비관리_v2.xlsx
+++ b/BUNT_finance/분트_인건비관리_v2.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'근무 기록'!$A$1:$H$288</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'지급 이력'!$A$1:$C$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'지급 이력'!$A$1:$D$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -93,12 +93,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -118,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -153,10 +147,7 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8607,12 +8598,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -8631,6 +8623,11 @@
           <t>지급여부</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>지급액</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -8646,6 +8643,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D2" s="12" t="n">
+        <v>1200000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -8661,6 +8661,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D3" s="12" t="n">
+        <v>528000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -8676,6 +8679,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D4" s="12" t="n">
+        <v>786000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -8691,6 +8697,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D5" s="12" t="n">
+        <v>1200000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -8706,6 +8715,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D6" s="12" t="n">
+        <v>240000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -8721,6 +8733,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D7" s="12" t="n">
+        <v>744000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -8736,6 +8751,9 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D8" s="12" t="n">
+        <v>600000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -8751,11 +8769,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D9" s="12" t="n">
+        <v>912000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>장예원</t>
+          <t>유은비</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -8766,11 +8787,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D10" s="12" t="n">
+        <v>240000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
@@ -8781,26 +8805,32 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D11" s="12" t="n">
+        <v>768000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>202504</v>
+        <v>202503</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>장예원</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
@@ -8811,11 +8841,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D13" s="12" t="n">
+        <v>792000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -8826,26 +8859,32 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D14" s="12" t="n">
+        <v>708000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>202505</v>
+        <v>202504</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>장예원</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
@@ -8856,11 +8895,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D16" s="12" t="n">
+        <v>1008000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
@@ -8871,26 +8913,32 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D17" s="12" t="n">
+        <v>516000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>202506</v>
+        <v>202505</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
@@ -8901,11 +8949,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D19" s="12" t="n">
+        <v>600000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>장예원</t>
+          <t>김채현</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -8916,11 +8967,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D20" s="12" t="n">
+        <v>120000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
@@ -8931,26 +8985,32 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D21" s="12" t="n">
+        <v>792000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>202507</v>
+        <v>202506</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
@@ -8961,11 +9021,14 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D23" s="12" t="n">
+        <v>672000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>김채현</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -8976,41 +9039,50 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D24" s="12" t="n">
+        <v>660000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>202508</v>
+        <v>202507</v>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>624000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>202508</v>
+        <v>202507</v>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B27" s="11" t="n">
@@ -9021,41 +9093,50 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D27" s="12" t="n">
+        <v>792000</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>김채현</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>202509</v>
+        <v>202508</v>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>648000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>202509</v>
+        <v>202508</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>1774000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -9066,41 +9147,50 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D30" s="12" t="n">
+        <v>588000</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>고경민</t>
+          <t>김채현</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>202510</v>
+        <v>202509</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>534000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>이진화</t>
+          <t>전민아</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
-        <v>202510</v>
+        <v>202509</v>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>전민아</t>
+          <t>고경민</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
@@ -9111,54 +9201,174 @@
           <t>O</t>
         </is>
       </c>
+      <c r="D33" s="12" t="n">
+        <v>1300000</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>고경민</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>202510</v>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>438000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>이진화</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>202510</v>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>202510</v>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>1848000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
         <v>202511</v>
       </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>이진화</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B38" s="11" t="n">
         <v>202511</v>
       </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>전민아</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B39" s="11" t="n">
         <v>202511</v>
       </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>1848000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>고경민</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>202512</v>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>이진화</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>202512</v>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>348000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>전민아</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>202512</v>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>1848000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C36"/>
+  <autoFilter ref="A1:D42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9186,21 +9396,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="14" t="n">
+      <c r="B1" s="13" t="n">
         <v>202502</v>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>← 월 선택</t>
         </is>
       </c>
-      <c r="J1" s="16">
+      <c r="J1" s="15">
         <f>DATE(INT(B1/100),MOD(B1,100),1)</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="J2" s="16">
+      <c r="J2" s="15">
         <f>EOMONTH(J1,0)</f>
         <v/>
       </c>
@@ -9262,7 +9472,7 @@
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>IF(B4="","",IF(C4="월급",'직원 마스터'!C2,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B4)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C4="월급",'직원 마스터'!C2,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F4" s="9">
@@ -9277,8 +9487,8 @@
         <f>IF(B4="","",'직원 마스터'!D2)</f>
         <v/>
       </c>
-      <c r="I4" s="17">
-        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B4)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I4" s="16">
+        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B4)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9296,7 +9506,7 @@
         <v/>
       </c>
       <c r="E5" s="9">
-        <f>IF(B5="","",IF(C5="월급",'직원 마스터'!C3,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B5)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C5="월급",'직원 마스터'!C3,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F5" s="9">
@@ -9311,8 +9521,8 @@
         <f>IF(B5="","",'직원 마스터'!D3)</f>
         <v/>
       </c>
-      <c r="I5" s="17">
-        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B5)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I5" s="16">
+        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B5)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9330,7 +9540,7 @@
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>IF(B6="","",IF(C6="월급",'직원 마스터'!C4,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B6)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C6="월급",'직원 마스터'!C4,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -9345,8 +9555,8 @@
         <f>IF(B6="","",'직원 마스터'!D4)</f>
         <v/>
       </c>
-      <c r="I6" s="17">
-        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B6)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I6" s="16">
+        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B6)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9364,7 +9574,7 @@
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>IF(B7="","",IF(C7="월급",'직원 마스터'!C5,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B7)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C7="월급",'직원 마스터'!C5,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -9379,8 +9589,8 @@
         <f>IF(B7="","",'직원 마스터'!D5)</f>
         <v/>
       </c>
-      <c r="I7" s="17">
-        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B7)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I7" s="16">
+        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B7)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9398,7 +9608,7 @@
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IF(B8="","",IF(C8="월급",'직원 마스터'!C6,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B8)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C8="월급",'직원 마스터'!C6,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F8" s="9">
@@ -9413,8 +9623,8 @@
         <f>IF(B8="","",'직원 마스터'!D6)</f>
         <v/>
       </c>
-      <c r="I8" s="17">
-        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B8)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I8" s="16">
+        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B8)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9432,7 +9642,7 @@
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IF(B9="","",IF(C9="월급",'직원 마스터'!C7,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B9)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C9="월급",'직원 마스터'!C7,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -9447,8 +9657,8 @@
         <f>IF(B9="","",'직원 마스터'!D7)</f>
         <v/>
       </c>
-      <c r="I9" s="17">
-        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B9)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I9" s="16">
+        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B9)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9466,7 +9676,7 @@
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IF(B10="","",IF(C10="월급",'직원 마스터'!C8,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B10)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C10="월급",'직원 마스터'!C8,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -9481,8 +9691,8 @@
         <f>IF(B10="","",'직원 마스터'!D8)</f>
         <v/>
       </c>
-      <c r="I10" s="17">
-        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B10)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I10" s="16">
+        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B10)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9500,7 +9710,7 @@
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IF(B11="","",IF(C11="월급",'직원 마스터'!C9,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B11)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C11="월급",'직원 마스터'!C9,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F11" s="9">
@@ -9515,8 +9725,8 @@
         <f>IF(B11="","",'직원 마스터'!D9)</f>
         <v/>
       </c>
-      <c r="I11" s="17">
-        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B11)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I11" s="16">
+        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B11)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9534,7 +9744,7 @@
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>IF(B12="","",IF(C12="월급",'직원 마스터'!C10,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A10)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B12)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C12="월급",'직원 마스터'!C10,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A10)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F12" s="9">
@@ -9549,8 +9759,8 @@
         <f>IF(B12="","",'직원 마스터'!D10)</f>
         <v/>
       </c>
-      <c r="I12" s="17">
-        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B12)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I12" s="16">
+        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B12)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9568,7 +9778,7 @@
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>IF(B13="","",IF(C13="월급",'직원 마스터'!C11,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A11)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500))))</f>
+        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B13)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C13="월급",'직원 마스터'!C11,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A11)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F13" s="9">
@@ -9583,37 +9793,37 @@
         <f>IF(B13="","",'직원 마스터'!D11)</f>
         <v/>
       </c>
-      <c r="I13" s="17">
-        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!C$2:C$86,MATCH(1,('지급 이력'!A$2:A$86=B13)*('지급 이력'!B$2:B$86=$B$1),0)),"X"))</f>
+      <c r="I13" s="16">
+        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B13)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="18">
         <f>SUM(E4:E13)</f>
         <v/>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <f>SUM(G4:G13)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>당월 총 인건비</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f>E15</f>
         <v/>
       </c>

--- a/BUNT_finance/분트_인건비관리_v2.xlsx
+++ b/BUNT_finance/분트_인건비관리_v2.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'근무 기록'!$A$1:$H$288</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'지급 이력'!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'지급 이력'!$A$1:$E$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8598,13 +8598,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -8628,6 +8629,11 @@
           <t>지급액</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>이름월키</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -8646,6 +8652,10 @@
       <c r="D2" s="12" t="n">
         <v>1200000</v>
       </c>
+      <c r="E2" s="10">
+        <f>A2&amp;B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -8664,6 +8674,10 @@
       <c r="D3" s="12" t="n">
         <v>528000</v>
       </c>
+      <c r="E3" s="10">
+        <f>A3&amp;B3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -8682,6 +8696,10 @@
       <c r="D4" s="12" t="n">
         <v>786000</v>
       </c>
+      <c r="E4" s="10">
+        <f>A4&amp;B4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -8700,6 +8718,10 @@
       <c r="D5" s="12" t="n">
         <v>1200000</v>
       </c>
+      <c r="E5" s="10">
+        <f>A5&amp;B5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -8718,6 +8740,10 @@
       <c r="D6" s="12" t="n">
         <v>240000</v>
       </c>
+      <c r="E6" s="10">
+        <f>A6&amp;B6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -8736,6 +8762,10 @@
       <c r="D7" s="12" t="n">
         <v>744000</v>
       </c>
+      <c r="E7" s="10">
+        <f>A7&amp;B7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -8754,6 +8784,10 @@
       <c r="D8" s="12" t="n">
         <v>600000</v>
       </c>
+      <c r="E8" s="10">
+        <f>A8&amp;B8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -8772,6 +8806,10 @@
       <c r="D9" s="12" t="n">
         <v>912000</v>
       </c>
+      <c r="E9" s="10">
+        <f>A9&amp;B9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -8790,6 +8828,10 @@
       <c r="D10" s="12" t="n">
         <v>240000</v>
       </c>
+      <c r="E10" s="10">
+        <f>A10&amp;B10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -8808,6 +8850,10 @@
       <c r="D11" s="12" t="n">
         <v>768000</v>
       </c>
+      <c r="E11" s="10">
+        <f>A11&amp;B11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -8826,6 +8872,10 @@
       <c r="D12" s="12" t="n">
         <v>1800000</v>
       </c>
+      <c r="E12" s="10">
+        <f>A12&amp;B12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -8844,6 +8894,10 @@
       <c r="D13" s="12" t="n">
         <v>792000</v>
       </c>
+      <c r="E13" s="10">
+        <f>A13&amp;B13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -8862,6 +8916,10 @@
       <c r="D14" s="12" t="n">
         <v>708000</v>
       </c>
+      <c r="E14" s="10">
+        <f>A14&amp;B14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -8880,6 +8938,10 @@
       <c r="D15" s="12" t="n">
         <v>1800000</v>
       </c>
+      <c r="E15" s="10">
+        <f>A15&amp;B15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -8898,6 +8960,10 @@
       <c r="D16" s="12" t="n">
         <v>1008000</v>
       </c>
+      <c r="E16" s="10">
+        <f>A16&amp;B16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -8916,6 +8982,10 @@
       <c r="D17" s="12" t="n">
         <v>516000</v>
       </c>
+      <c r="E17" s="10">
+        <f>A17&amp;B17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -8934,6 +9004,10 @@
       <c r="D18" s="12" t="n">
         <v>1800000</v>
       </c>
+      <c r="E18" s="10">
+        <f>A18&amp;B18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -8952,6 +9026,10 @@
       <c r="D19" s="12" t="n">
         <v>600000</v>
       </c>
+      <c r="E19" s="10">
+        <f>A19&amp;B19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -8970,6 +9048,10 @@
       <c r="D20" s="12" t="n">
         <v>120000</v>
       </c>
+      <c r="E20" s="10">
+        <f>A20&amp;B20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -8988,6 +9070,10 @@
       <c r="D21" s="12" t="n">
         <v>792000</v>
       </c>
+      <c r="E21" s="10">
+        <f>A21&amp;B21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -9006,6 +9092,10 @@
       <c r="D22" s="12" t="n">
         <v>1800000</v>
       </c>
+      <c r="E22" s="10">
+        <f>A22&amp;B22</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -9024,6 +9114,10 @@
       <c r="D23" s="12" t="n">
         <v>672000</v>
       </c>
+      <c r="E23" s="10">
+        <f>A23&amp;B23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -9042,6 +9136,10 @@
       <c r="D24" s="12" t="n">
         <v>660000</v>
       </c>
+      <c r="E24" s="10">
+        <f>A24&amp;B24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -9060,6 +9158,10 @@
       <c r="D25" s="12" t="n">
         <v>624000</v>
       </c>
+      <c r="E25" s="10">
+        <f>A25&amp;B25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -9078,6 +9180,10 @@
       <c r="D26" s="12" t="n">
         <v>1800000</v>
       </c>
+      <c r="E26" s="10">
+        <f>A26&amp;B26</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -9096,6 +9202,10 @@
       <c r="D27" s="12" t="n">
         <v>792000</v>
       </c>
+      <c r="E27" s="10">
+        <f>A27&amp;B27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -9114,6 +9224,10 @@
       <c r="D28" s="12" t="n">
         <v>648000</v>
       </c>
+      <c r="E28" s="10">
+        <f>A28&amp;B28</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -9132,6 +9246,10 @@
       <c r="D29" s="12" t="n">
         <v>1774000</v>
       </c>
+      <c r="E29" s="10">
+        <f>A29&amp;B29</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -9150,6 +9268,10 @@
       <c r="D30" s="12" t="n">
         <v>588000</v>
       </c>
+      <c r="E30" s="10">
+        <f>A30&amp;B30</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -9168,6 +9290,10 @@
       <c r="D31" s="12" t="n">
         <v>534000</v>
       </c>
+      <c r="E31" s="10">
+        <f>A31&amp;B31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -9186,6 +9312,10 @@
       <c r="D32" s="12" t="n">
         <v>1800000</v>
       </c>
+      <c r="E32" s="10">
+        <f>A32&amp;B32</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -9204,6 +9334,10 @@
       <c r="D33" s="12" t="n">
         <v>1300000</v>
       </c>
+      <c r="E33" s="10">
+        <f>A33&amp;B33</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -9222,6 +9356,10 @@
       <c r="D34" s="12" t="n">
         <v>438000</v>
       </c>
+      <c r="E34" s="10">
+        <f>A34&amp;B34</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -9240,6 +9378,10 @@
       <c r="D35" s="12" t="n">
         <v>480000</v>
       </c>
+      <c r="E35" s="10">
+        <f>A35&amp;B35</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -9258,6 +9400,10 @@
       <c r="D36" s="12" t="n">
         <v>1848000</v>
       </c>
+      <c r="E36" s="10">
+        <f>A36&amp;B36</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -9276,6 +9422,10 @@
       <c r="D37" s="12" t="n">
         <v>1300000</v>
       </c>
+      <c r="E37" s="10">
+        <f>A37&amp;B37</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -9294,6 +9444,10 @@
       <c r="D38" s="12" t="n">
         <v>480000</v>
       </c>
+      <c r="E38" s="10">
+        <f>A38&amp;B38</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -9312,6 +9466,10 @@
       <c r="D39" s="12" t="n">
         <v>1848000</v>
       </c>
+      <c r="E39" s="10">
+        <f>A39&amp;B39</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -9330,6 +9488,10 @@
       <c r="D40" s="12" t="n">
         <v>1300000</v>
       </c>
+      <c r="E40" s="10">
+        <f>A40&amp;B40</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -9348,6 +9510,10 @@
       <c r="D41" s="12" t="n">
         <v>348000</v>
       </c>
+      <c r="E41" s="10">
+        <f>A41&amp;B41</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -9366,9 +9532,13 @@
       <c r="D42" s="12" t="n">
         <v>1848000</v>
       </c>
+      <c r="E42" s="10">
+        <f>A42&amp;B42</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D42"/>
+  <autoFilter ref="A1:E42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9472,7 +9642,7 @@
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B4)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C4="월급",'직원 마스터'!C2,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B4&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C4="월급",'직원 마스터'!C2,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A2)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F4" s="9">
@@ -9488,7 +9658,7 @@
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B4)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B4="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B4&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9506,7 +9676,7 @@
         <v/>
       </c>
       <c r="E5" s="9">
-        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B5)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C5="월급",'직원 마스터'!C3,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B5&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C5="월급",'직원 마스터'!C3,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A3)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F5" s="9">
@@ -9522,7 +9692,7 @@
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B5)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B5="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B5&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9540,7 +9710,7 @@
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B6)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C6="월급",'직원 마스터'!C4,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B6&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C6="월급",'직원 마스터'!C4,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A4)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -9556,7 +9726,7 @@
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B6)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B6="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B6&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9574,7 +9744,7 @@
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B7)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C7="월급",'직원 마스터'!C5,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B7&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C7="월급",'직원 마스터'!C5,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A5)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -9590,7 +9760,7 @@
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B7)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B7="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B7&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9608,7 +9778,7 @@
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B8)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C8="월급",'직원 마스터'!C6,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B8&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C8="월급",'직원 마스터'!C6,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A6)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F8" s="9">
@@ -9624,7 +9794,7 @@
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B8)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B8="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B8&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9642,7 +9812,7 @@
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B9)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C9="월급",'직원 마스터'!C7,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B9&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C9="월급",'직원 마스터'!C7,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A7)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -9658,7 +9828,7 @@
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B9)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B9="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B9&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9676,7 +9846,7 @@
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B10)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C10="월급",'직원 마스터'!C8,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B10&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C10="월급",'직원 마스터'!C8,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A8)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -9692,7 +9862,7 @@
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B10)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B10="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B10&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9710,7 +9880,7 @@
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B11)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C11="월급",'직원 마스터'!C9,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B11&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C11="월급",'직원 마스터'!C9,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A9)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F11" s="9">
@@ -9726,7 +9896,7 @@
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B11)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B11="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B11&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9744,7 +9914,7 @@
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B12)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C12="월급",'직원 마스터'!C10,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A10)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B12&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C12="월급",'직원 마스터'!C10,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A10)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F12" s="9">
@@ -9760,7 +9930,7 @@
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B12)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B12="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B12&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
@@ -9778,7 +9948,7 @@
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(1,('지급 이력'!A$2:A$92=B13)*('지급 이력'!B$2:B$92=$B$1),0)),IF(C13="월급",'직원 마스터'!C11,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A11)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
+        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!D$2:D$92,MATCH(B13&amp;$B$1,'지급 이력'!E$2:E$92,0)),IF(C13="월급",'직원 마스터'!C11,SUMPRODUCT(('근무 기록'!B$2:B$500='직원 마스터'!A11)*('근무 기록'!A$2:A$500&gt;=J$1)*('근무 기록'!A$2:A$500&lt;=J$2)*('근무 기록'!F$2:F$500)))))</f>
         <v/>
       </c>
       <c r="F13" s="9">
@@ -9794,7 +9964,7 @@
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(1,('지급 이력'!A$2:A$92=B13)*('지급 이력'!B$2:B$92=$B$1),0)),"X"))</f>
+        <f>IF(B13="","",IFERROR(INDEX('지급 이력'!C$2:C$92,MATCH(B13&amp;$B$1,'지급 이력'!E$2:E$92,0)),"X"))</f>
         <v/>
       </c>
     </row>
